--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -87,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -103,6 +108,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,13 +474,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -518,625 +524,805 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>用法：Step 2 评估前与项目 adjudications.md 同读；源文档 docs/质量检查项清单.md</t>
+          <t>用法：Step 2 评估前与项目 adjudications.md 同读；源文档 docs/质量检查项清单.md（更新以 md 为准，本表由 scripts/gen_checklist_xlsx.py 重导）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>0512 失分画像（优先级依据）</t>
+          <t>规则来源代号（全表通用，〔〕标注）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>代号</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>重复(不罚分)</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>加权罚分</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>占比</t>
+          <t>出处文档</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Mistranslation</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>783</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>85.6%</t>
+          <t>SKILL</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SKILL.md（现行 skill 主文档；R 号=docs/LQE质量标准优化报告.html 的 R1-R30 整改项，上游分析=差距分析 GAP-06）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Terminology</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>9.8%</t>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>projects/wwm/sg.txt（WWM 权威风格指南）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Company style</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>2.8%</t>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>projects/wwm/adjudications.md 0512 前旧段（历史 LQE 经验）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Unidiomatic</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>1.0%</t>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>docs/差距分析.md（GAP-01~08）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Inconsistency</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>0.8%</t>
+          <t>调研</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>docs/调研-行业标准证据简报.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>其余 12 类</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>0512</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>0512 人工 LQE 报告·错误明细＋LQA Scorecard sheet（本次新证据）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" s="5" t="n">
+          <t>0512def</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>同报告 Error Definition sheet（客户权威错误定义表，含逐类三档严重度例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>LQA</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>客户 LQA 译员评估模板（How to Fill / Score-for evaluator sheet，本次新证据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>0512 失分画像（优先级依据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>重复(不罚分)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>加权罚分</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Mistranslation</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>915</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>41 个 Critical 构成：对联 26＋对联流对话 3＋玩法规则文本 7＋活动名/考勤 UI 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>教训① 85% 失分来自 Mistranslation——重灾区是成组文本拆单句直译与规则文本语义错</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>教训② 确定性类（Markup/Length/标点/拼写/漏多译）零错，pre-check 路线有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>教训③ 下一批输入《玩法数据表_题目表_皇宫以外内容.xlsx》与对联块同型，最高危，必须成组评估</t>
+      <c r="E22" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>783</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>85.6%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>评估元规则（每条错误先过）</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Terminology</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Company style</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>三点法则</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>准确＋合规（SG/指令/术语）＋合语法→视为正确，偏好性改写不计错（至多 Neutral 建议）。防误报第一道闸（客户 LQA 模板）</t>
+          <t>Unidiomatic</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>单一归属＋存疑取重</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>按 SKILL.md 归类决策表取最具体一类；Minor/Major 拿不准取 Major</t>
+          <t>Inconsistency</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>0.8%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Word Choice 边界</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>意思错→Mistranslation；意思对但有更优词→Unidiomatic(Min) 或 Neutral（客户模板明文）</t>
+          <t>其余 12 类</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>严重度三档锚</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Minor=可察觉不误导；Major=很可能误导玩家/损公信；Critical=投诉/法务/功能破坏/高曝光面</t>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>915</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>41 个 Critical 构成：对联 26＋对联流对话 3＋玩法规则文本 7＋活动名/考勤 UI 5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>计分与流程规则</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>教训① 85% 失分来自 Mistranslation——重灾区是成组文本拆单句直译与规则文本语义错</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>教训② 确定性类（Markup/Length/标点/拼写/漏多译）零错，pre-check 路线有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>教训③ 下一批输入《玩法数据表_题目表_皇宫以外内容.xlsx》与对联块同型，最高危，必须成组评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>评估元规则（每条错误先过）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>规则</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>证据</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>重复错误</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>记录（Repeated=YES）不罚分，首次全额</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>0512：34 条 rep 罚分=0（GAP-07 落定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>阈值分层</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>TEP/MTPE=98；润色/二审=99</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>客户 Error Definition 表；profile.threshold 已支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>严重度分值</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>0/1/5/10（客户=LISA 制，非 MQM 25）——GAP-03 的 MQM 调参不采</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>两报告一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>score=1−Σ(加权罚分)/词数，与客户完全一致；0512 词数口径=target-words(5,314)</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>0512 复算吻合</t>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>规则来源</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>成组文本</t>
+          <t>三点法则</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>对联/题目/谜题按组评估：上下联对仗＋押韵＋题目-答案可配对；拆单句直译=组级 Critical</t>
+          <t>准确＋合规（SG/指令/术语）＋合语法→视为正确，偏好性改写不计错（至多 Neutral 建议）。防误报第一道闸</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>0512 对联块 26 Cri</t>
+          <t>LQA How to Fill（新增）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>内容桶倾向</t>
+          <t>单一归属＋存疑取重</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>规则说明→错译默认 Cri；UI 短串→Unidiomatic/style 主导；诗句 banner→Company style 重写权</t>
+          <t>按归类决策表取最具体一类；Minor/Major 拿不准取 Major</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>0512 分布</t>
+          <t>SKILL §归类决策规则←调研 §1.4 J2450 元规则（沿用）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>Word Choice 边界</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>意思错→Mistranslation；意思对但有更优词→Unidiomatic(Min) 或 Neutral</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>LQA 模板明文（新增）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>严重度三档锚</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Minor=可察觉不误导；Major=很可能误导玩家/损公信；Critical=投诉/法务/功能破坏/高曝光面</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>SKILL 严重度判定（沿用）＋0512def 逐类细化</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>计分与流程规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>规则来源</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>重复错误</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>记录（Repeated=YES）不罚分，首次全额</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0512 Scorecard 实证（新增）；问题背景=GAP-07</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>34 条 rep 罚分=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>阈值分层</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>TEP/MTPE=98；润色/二审=99</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>数值=0512def（新增）；分层概念上游=调研 §3 DQF</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>客户 Error Definition 表；profile.threshold 已支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>严重度分值</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>0/1/5/10（客户=LISA 制，非 MQM 25）——GAP-03 的 MQM 调参不采</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>SKILL 沿用；与 0512def 一致</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>两报告一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>score=1−Σ(加权罚分)/词数；词数口径=target-words</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>SKILL 沿用；与 0512def 完全一致</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>0512 复算吻合（5,314 词）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>成组文本</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>对联/题目/谜题按组评估：上下联对仗＋押韵＋题目-答案可配对；拆单句直译=组级 Critical</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0512 错误明细（全新）</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>对联块 26 Cri</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>内容桶倾向</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>规则说明→错译默认 Cri；UI 短串→Unidiomatic/style 主导；诗句 banner→Company style 重写权</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>概念=调研 §2.3/GAP-05；具体倾向=0512（新增）</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>0512 判级分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
           <t>报告解析</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>corrected 列可为 #N/A（审校未给改稿）；Repeated 列 YES/NO</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>0512 实表</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0512 实表（新增）</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>r129 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>待落地变更</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>变更</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
+    <row r="53">
+      <c r="A53" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>重复错误去重计分（N4）</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_calc.py</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>待 go</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
+    <row r="54">
+      <c r="A54" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>拼音残留（N1）＋同源异译（N2）</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_io.py pre-check</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>待 go</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
+    <row r="55">
+      <c r="A55" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>罗马数字 custom（N3）</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>projects/wwm/checks.json</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>待 go</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
+    <row r="56">
+      <c r="A56" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>0512 术语/风格裁决注入</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>projects/wwm/adjudications.md</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
+    <row r="57">
+      <c r="A57" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Step 2 评估提示引用本清单</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>SKILL.md</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>待 go</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
+    <row r="58">
+      <c r="A58" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>题目表/对联输入带组上下文</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>lqe_io.py read / Step 2 流程</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>待 go（下批题目表前急需）</t>
         </is>
@@ -1153,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1161,9 +1347,10 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,10 +1386,15 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>规则来源</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>评估关注点</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>落地</t>
         </is>
@@ -1236,15 +1428,20 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
+          <t>SKILL Step1.5 初版</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
           <t>指令允许保留项除外</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1278,15 +1475,20 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
+          <t>SKILL Step1.5</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
           <t>口径与词数基准联动（source-chars 时仍计分）</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1320,15 +1522,20 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
+          <t>SKILL 初版＋SG 标点</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
           <t>项目可关（nrc-en 已关）</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1362,15 +1569,20 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
+          <t>SKILL 初版＋SG Markup</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
           <t>相对位置也须一致，非仅数量</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1404,15 +1616,20 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>0512 实证：「{}天后领取{}」丢一个占位符被人工判 Mistranslation Critical——占位符错按客户口径是最重级</t>
+          <t>SKILL 初版＋SG Markup</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>0512 实证：「{}天后领取{}」丢一个占位符被人工判 Mistranslation Critical——占位符错按客户口径是最重级〔0512〕</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1446,15 +1663,20 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
+          <t>SKILL R1 整改←GAP-06</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
           <t>命名/带索引占位符允许重排</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1488,11 +1710,16 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
+          <t>现行沿用</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>SKILL 初版＋SG</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1526,15 +1753,20 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
+          <t>SKILL R6 整改←GAP-06</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
           <t>仅源含阿拉伯数字触发；中文数字不误报；语境误报可移除</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1568,15 +1800,20 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
+          <t>max-length=SKILL R3←GAP-06；1.5× 回退=初版</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
           <t>max-length 列优先；无列时仅非 CJK 源回退</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1610,11 +1847,16 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr">
+          <t>现行沿用</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>SKILL 初版＋SG 数字</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1648,11 +1890,16 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr">
+          <t>现行沿用</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>SKILL R5 整改←GAP-06</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1686,11 +1933,16 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr">
+          <t>现行沿用</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>SKILL R5 整改＋SG 半角标点</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1724,15 +1976,20 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>现行沿用</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>[TB:status]：Approved 硬判；New/WorkingTB 语境甄别；泛词命中≠错误</t>
+          <t>SKILL 初版；TB:status 机制=项目档案</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>[TB:status]：Approved 硬判；New/WorkingTB 语境甄别；泛词命中≠错误〔ADJ〕</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1771,10 +2028,15 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
+          <t>0512 全新发现</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
           <t>target 含 2+ 连续拼音音节大写词且不在官方拼音白名单（Kaifeng/Qinghe/Jianghu/Fu Shen/Xuanyu…）。0512：画卯→Mark Mao、平安→Ping'an 均 Cri。半确定：regex 初筛＋AI 复核</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>pre-check 待落地</t>
         </is>
@@ -1813,10 +2075,15 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
+          <t>GAP-06「文件内一致性」首次落清单；0512 实证支持</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
           <t>文件内相同 source 不同 target；反向（相同 target 不同 source）一并报</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>pre-check 待落地</t>
         </is>
@@ -1855,10 +2122,15 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
+          <t>0512 改稿风格</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
           <t>序号/卷号用 Unicode Ⅰ Ⅱ Ⅲ，非 ASCII I/II/III（0512：其一→Ⅰ、Volume Ⅱ）</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>wwm checks.json 待落地</t>
         </is>
@@ -1897,10 +2169,15 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>同源＋同译＋同错仅首次计分，其余标 Repeated=YES 不罚分。0512 实证客户策略（34 条 rep 罚分=0）</t>
+          <t>问题=GAP-07 死列；策略=0512 实证落定</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>同源＋同译＋同错仅首次计分，其余标 Repeated=YES 不罚分（0512：34 条 rep 罚分=0）</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>lqe_calc.py 待落地</t>
         </is>
@@ -1917,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1925,83 +2202,51 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="88" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>子类体系/权重/强制 Major/严重度 0-1-5-10 全部沿用〔SKILL §LQE错误分类；七父维度=GAP-01/02 整改〕；「严重度梯度」列统一取自〔0512def〕；关注点逐条〔〕标来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>父维度</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>子类别</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>强制严重度</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>0512 计分</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>评估关注点</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>严重度梯度（客户锚）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Mistranslation 错译</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Min2·Maj22(+8rep)·Cri41(+5rep)＝最大失分源</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>• 专名↔通名双向误判：拼音残留（画卯→Roll Call，×Mark Mao；平安→Peace，×Ping'an）；通名实体化幻觉（年年≠Niannian；岁月长安≠Chang'an；紫色团花=purple flower，×Epic Flower）
-• 玩法规则文本逐条核：数值/上限/门槛（铜筹折算上限2000）、阶段流程序、机制词（多轮循环=Round-robin，×Rotating）、奖励归属与返还条件——客户一律 Critical
-• 操作指引动作语义：技能效果的对象与方式（复原巨石使其停下≠restore…to a halt；招式=any attack，×a Move）
-• 价格/概率语义词不可丢：折扣价、有机会获得（客户 Cri 例：源「有机会获得[68金币]」译 contains）；回復≠receive
-• 升 Cri 信号：误导玩家决策的规则文/题目-答案失配/占位符语义错位/经济敏感</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Min=误读但贴近源｜Maj=译错（关卡→Close Card）｜Cri=日期/规则/内容错致投诉法务</t>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>评估关注点（〔〕=规则来源）</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>严重度梯度（源:0512def）</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2258,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Omission 漏译</t>
+          <t>Mistranslation 错译</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -2026,18 +2271,21 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Min2·Maj22(+8rep)·Cri41(+5rep)＝最大失分源</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>• 限定词清点：任意/1次/仅/同时/最高/每（0512 近失：a Sword Trial 丢「任意」）
-• 进度/资格条件（充值/达标/解锁）丢失即 Cri</t>
+          <t>• 专名↔通名双向误判：拼音残留（画卯→Roll Call，×Mark Mao；平安→Peace，×Ping'an）；通名实体化幻觉（年年≠Niannian；岁月长安≠Chang'an；紫色团花=purple flower，×Epic Flower）〔0512〕
+• 玩法规则文本逐条核：数值/上限/门槛（铜筹折算上限2000）、阶段流程序、机制词（多轮循环=Round-robin，×Rotating）、奖励归属与返还条件——客户一律 Critical〔0512〕
+• 操作指引动作语义：技能效果的对象与方式（复原巨石使其停下≠restore…to a halt；招式=any attack，×a Move）〔0512〕
+• 价格/概率语义词不可丢：折扣价、有机会获得（Cri 例：源「有机会获得[68金币]」译 contains）；回復≠receive〔0512＋0512def〕
+• 升 Cri 信号：误导玩家决策的规则文/题目-答案失配/占位符语义错位/经济敏感〔0512〕</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Min=丢衔接词｜Maj=丢改义成分（范围内的敌人→all enemies）｜Cri=丢进度资格关键信息</t>
+          <t>Min=误读但贴近源｜Maj=译错（关卡→Close Card）｜Cri=日期/规则/内容错致投诉法务</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2297,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Addition 多译</t>
+          <t>Omission 漏译</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -2067,13 +2315,13 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>• 贴源过译与偏离区分
-• 勿引入不存在的玩法元素（单体伤害→all enemies）</t>
+          <t>• 限定词清点：任意/1次/仅/同时/最高/每（0512 近失：a Sword Trial 丢「任意」）〔0512〕
+• 进度/资格条件（充值/达标/解锁）丢失即 Cri〔0512def〕</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Min=过译仍贴源｜Maj=偏离源｜Cri=引入不存在玩法元素/招致投诉破坏沉浸</t>
+          <t>Min=丢衔接词｜Maj=丢改义成分（范围内的敌人→all enemies）｜Cri=丢进度资格关键信息</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2333,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Untranslated 未翻译</t>
+          <t>Addition 多译</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -2093,35 +2341,35 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>始终Maj</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0（pre-check 拦截）</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>• 拼音输出≠已翻译——按 Mistranslation Cri 处理（N1）
-• 英文源原样复制也算未译（不止中文残留）</t>
+          <t>• 贴源过译与偏离区分〔0512def〕
+• 勿引入不存在的玩法元素（单体伤害→all enemies）〔0512def〕</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>始终 Major</t>
+          <t>Min=过译仍贴源｜Maj=偏离源｜Cri=引入不存在玩法元素/招致投诉破坏沉浸</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Terminology</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Terminology 术语</t>
+          <t>Untranslated 未翻译</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -2134,18 +2382,13 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Maj12(+8rep)＝第二失分源</t>
+          <t>0（pre-check 拦截）</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>• 活动/玩法/界面入口名逐字对官方库与已上线译名：皇宫寻宝=Imperial Palace Treasure Hunt（自创=Maj）；御前练兵=Imperial Drill
-• 成对称号体系成对取：新锐|新兵=Recruit／老将|老兵=Veteran（×New Edge/Old General）
-• 人名代号查角色档：青=Halcyon（×Qing 直拼）
-• 同物跨段同名：手札统一 Journal（×Note）
-• 过度术语化=错：通名勿造专名（异色灵蝶=strangely colored butterflies，×Spectral Butterfly）
-• 系列名格式：赋神·乘桴归梦=Fu Shen - Rippling Dream（·→" - "，系列前缀保留）
-• 强制定译 19 条见 projects/wwm/adjudications.md《0512 裁决》（太极=Cosmic Reversal ×Tai Chi 等）；泛词命中按语境甄别</t>
+          <t>• 拼音输出≠已翻译——按 Mistranslation Cri 处理（N1）〔0512〕
+• 英文源原样复制也算未译（不止中文残留）〔GAP-06 未译扩展〕</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2157,12 +2400,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Terminology</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Inconsistency 一致性</t>
+          <t>Terminology 术语</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -2170,24 +2413,28 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>始终Maj</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Min5(+2rep)</t>
+          <t>Maj12(+8rep)＝第二失分源</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>• 平行句族统一句型：任务/成就列表同模板（Complete any X once with a Veteran/Recruit 族）
-• 任务名引用格式统一（Lost Chapter quest: X）
-• 涉术语表词条的冲突归 Terminology，其余归此</t>
+          <t>• 活动/玩法/界面入口名逐字对官方库与已上线译名：皇宫寻宝=Imperial Palace Treasure Hunt（自创=Maj）；御前练兵=Imperial Drill〔0512〕
+• 成对称号体系成对取：新锐|新兵=Recruit／老将|老兵=Veteran（×New Edge/Old General）〔0512〕
+• 人名代号查角色档：青=Halcyon（×Qing 直拼）〔0512〕
+• 同物跨段同名：手札统一 Journal（×Note）〔0512〕
+• 过度术语化=错：通名勿造专名（异色灵蝶=strangely colored butterflies，×Spectral Butterfly）〔0512〕
+• 系列名格式：赋神·乘桴归梦=Fu Shen - Rippling Dream（系列前缀保留〔0512〕；·→" - "=SG 既有规则〔SG〕）
+• 强制定译 19 条见 projects/wwm/adjudications.md《0512 裁决》〔0512〕；泛词命中按语境甄别〔ADJ 沿用〕</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Min=拼写大小写语气不一（approx./approximately 混用）｜Maj=术语混用致误解（hero/protagonist/main character）</t>
+          <t>始终 Major</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2446,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Grammar 语法</t>
+          <t>Inconsistency 一致性</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -2212,18 +2459,19 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Min5(+2rep)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>• 主谓一致/时态/冠词
-• 占位符邻接可数名词用「{} day(s)」型复数</t>
+          <t>• 平行句族统一句型：任务/成就列表同模板（Complete any X once with a Veteran/Recruit 族）〔0512〕
+• 任务名引用格式统一（Lost Chapter quest: X）〔0512〕
+• 涉术语表词条的冲突归 Terminology，其余归此〔SKILL 归类决策表沿用〕</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Min=显粗心（Me and my friends are…）｜Maj=损公信（The lego set are nice）｜Cri=灾难性后果</t>
+          <t>Min=拼写大小写语气不一（approx./approximately 混用）｜Maj=术语混用致误解（hero/protagonist/main character）</t>
         </is>
       </c>
     </row>
@@ -2235,11 +2483,11 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Punctuation 标点</t>
+          <t>Grammar 语法</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -2248,18 +2496,18 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0（pre-check 盖大半）</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>• 半角标点、对齐源标点（pre-check/custom 已盖大半）
-• 长句逗号缺失影响可读性</t>
+          <t>• 主谓一致/时态/冠词〔0512def/LQA 通则〕
+• 占位符邻接可数名词用「{} day(s)」型复数〔0512〕</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Min=错但可懂｜Maj=改句意（Let's eat, Timmy→Let's eat Timmy）｜Cri=金额标点致事实错误</t>
+          <t>Min=显粗心（Me and my friends are…）｜Maj=损公信（The lego set are nice）｜Cri=灾难性后果</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2519,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Spelling 拼写</t>
+          <t>Punctuation 标点</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -2284,34 +2532,34 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0（pre-check 盖大半）</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>• Equipments/Acheive/Entrence 型错拼
-• 易混词 accept/except、then/than、your/you're=Maj</t>
+          <t>• 半角标点、对齐源标点（pre-check/custom 已盖大半）〔SG＋SKILL 沿用〕
+• 长句逗号缺失影响可读性〔LQA〕</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Min=粗心错拼｜Maj=损公信易混词｜Cri=灾难性（pubic library）</t>
+          <t>Min=错但可懂｜Maj=改句意（Let's eat, Timmy→Let's eat Timmy）｜Cri=金额标点致事实错误</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Company style 公司风格</t>
+          <t>Spelling 拼写</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -2320,21 +2568,18 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Min12·Maj1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>• 句中通名小写：accept a quest / the treasure（×句中 Accept a Quest）——Title Mode 仅限标题位
-• 序号/卷号 Unicode 罗马数字（N3）
-• 括号体系：设施/可放置物名 [Stove]（×「」原样、×#Y"X"#E 引号式）
-• 诗句/banner 有押韵节奏重写权（九天阊阖联→bold/gold 韵对）；过度直译判此类
-• 禁古英语/网络俚语/UI 语气进剧情（SG 明文违反才归此，无明文归 Unidiomatic）</t>
+          <t>• Equipments/Acheive/Entrence 型错拼〔0512def〕
+• 易混词 accept/except、then/than、your/you're=Maj〔0512def〕</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Min=Oxford comma/大小写规则未followed｜Maj=语域错置（古风项目用 Sup, Harry?）</t>
+          <t>Min=粗心错拼｜Maj=损公信易混词｜Cri=灾难性（pubic library）</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2591,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Unidiomatic 不合语言习惯</t>
+          <t>Company style 公司风格</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -2359,35 +2604,37 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Min6(+11rep)</t>
+          <t>Min12·Maj1</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>• UI 短句自然化模板：Continue Completing &lt;X&gt;→Continue completing the X quest（去尖括号＋补通名 quest＋句子化大小写）——0512 同一模式重复 12 次
-• 直译腔标志：Warm Tips / Successfully Claimed 型
-• 三档标尺（客户 Naturalness）：母语者难懂／直译但可懂／好文笔——仅前两档计错</t>
+          <t>• 句中通名小写：accept a quest / the treasure（×句中 Accept a Quest）〔0512；Title/Sentence Mode 本体=SG 沿用〕
+• 序号/卷号 Unicode 罗马数字（N3）〔0512〕
+• 括号体系：设施/可放置物名 [Stove]（×「」原样、×#Y"X"#E 引号式）〔0512〕
+• 诗句/banner 有押韵节奏重写权（九天阊阖联→bold/gold 韵对）；过度直译判此类〔0512〕
+• 禁古英语/网络俚语/UI 语气进剧情〔SG 沿用〕；SG 明文违反才归此，无明文归 Unidiomatic〔SKILL 归类决策表沿用〕</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Min=不地道但可懂（Successfully Claimed）｜Maj=不地道且致困惑（Warm Tips）｜Cri=冒犯或彻底破坏沉浸（You no go. I go for you!）</t>
+          <t>Min=Oxford comma/大小写规则未循｜Maj=语域错置（古风项目用 Sup, Harry?）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Locale convention</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Locale convention 语言环境约定</t>
+          <t>Unidiomatic 不合语言习惯</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -2396,34 +2643,35 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Min6(+11rep)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>• 日期防歧义拼写月份（6/5/2023→May 6, 2023）
-• 货币符号与币种一致</t>
+          <t>• UI 短句自然化模板：Continue Completing &lt;X&gt;→Continue completing the X quest（去尖括号＋补通名 quest＋句子化大小写）——0512 同一模式重复 12 次〔0512；非代码禁 &lt;&gt; 旧规=ADJ〕
+• 直译腔标志：Warm Tips / Successfully Claimed 型〔0512def〕
+• 三档标尺：母语者难懂／直译但可懂／好文笔——仅前两档计错〔LQA Naturalness，新增〕</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Min=格式少见仍可懂｜Maj=影响理解｜Cri=币种错（¥299→$299）致法务/财务风险</t>
+          <t>Min=不地道但可懂（Successfully Claimed）｜Maj=不地道且致困惑（Warm Tips）｜Cri=冒犯或彻底破坏沉浸（You no go. I go for you!）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Audience Appropriateness（客户父类=Verity）</t>
+          <t>Locale convention</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Culture specific reference 文化特定所指</t>
+          <t>Locale convention 语言环境约定</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -2437,25 +2685,25 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>• 源文化梗错置目标受众（520、圣诞吃苹果）
-• 冒犯/涉政/禁忌=Cri</t>
+          <t>• 日期防歧义拼写月份（6/5/2023→May 6, 2023）〔0512def〕
+• 货币符号与币种一致〔0512def〕</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Min=文化梗略怪｜Maj=过于小众致困惑｜Cri=冒犯/政治敏感</t>
+          <t>Min=格式少见仍可懂｜Maj=影响理解｜Cri=币种错（¥299→$299）致法务/财务风险</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Audience Appropriateness</t>
+          <t>Audience Appropriateness（客户父类=Verity）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Audience appropriateness 受众适配</t>
+          <t>Culture specific reference 文化特定所指</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2468,30 +2716,30 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0（本 skill 独有子类）</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>• 语域/世界观口吻（仙侠敬语→现代俚语）
-• 准确但不合受众期待</t>
+          <t>• 源文化梗错置目标受众（520、圣诞吃苹果）〔0512def〕
+• 冒犯/涉政/禁忌=Cri〔0512def〕</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>参照 Company style/Unidiomatic 梯度按影响定级</t>
+          <t>Min=文化梗略怪｜Maj=过于小众致困惑｜Cri=冒犯/政治敏感</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Design &amp; Markup</t>
+          <t>Audience Appropriateness</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Markup 标记</t>
+          <t>Audience appropriateness 受众适配</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2499,22 +2747,23 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>始终Maj</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0（pre-check 盖）</t>
+          <t>0（本 skill 独有子类）</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>• 色标相对位置、{} 数量与顺序、\n 保留</t>
+          <t>• 语域/世界观口吻（仙侠敬语→现代俚语）〔SKILL←GAP-01 整改沿用〕
+• 准确但不合受众期待〔SKILL 沿用〕</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>始终 Major</t>
+          <t>参照 Company style/Unidiomatic 梯度按影响定级</t>
         </is>
       </c>
     </row>
@@ -2526,11 +2775,11 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Length 长度</t>
+          <t>Markup 标记</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
@@ -2544,7 +2793,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>• max-length 列优先；超长截断风险</t>
+          <t>• 色标相对位置、{} 数量与顺序、\n 保留〔SKILL＋SG 沿用〕</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2556,12 +2805,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Design &amp; Markup</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Other 其他</t>
+          <t>Length 长度</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -2569,20 +2818,55 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>始终Maj</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0（pre-check 盖）</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>• max-length 列优先；超长截断风险〔SKILL R3←GAP-06〕</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>始终 Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Other 其他</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>• 兜底；先过单一归属表再落此</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>• 兜底；先过单一归属表再落此〔SKILL 沿用〕</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -474,12 +474,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -496,833 +496,725 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>更新 2026-06-11</t>
+          <t>更新 2026-06-11。参考仅三份（来源标注用〔〕）：</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>证据① 0512《【AI】【英】globaltrunk【0511新增】_LQE Report》＝WWM 中→英 AI 译文人工 LQE（5,314 词，82.78 FAIL，计分错误 101＋重复 34）</t>
+          <t>〔Skill〕现行 skill（SKILL.md：pre-check 13 项、17 子类、权重/强制 Major、公式、归类决策、严重度判定）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>证据② 客户《LQA template to evaluate cooperating translators》（译员评估模板；全文提取 projects/nrc-common/LQA_template_extract.txt）</t>
+          <t>〔LQE报告〕0512《【AI】【英】globaltrunk【0511新增】_LQE Report.xlsx》＝WWM 中→英 AI 译文人工 LQE（5,314 词，82.78 FAIL，计分错误 101＋重复 34；含错误明细/评分卡/客户错误定义表）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>基线：SKILL.md 现行 pre-check＋17 子类；docs/调研-行业标准证据简报.md；docs/差距分析.md</t>
+          <t>〔LQA模板〕《LQA template to evaluate current cooperating translators.xlsx》（客户译员评估模板）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>〔Skill〕=沿用现行体系；〔LQE报告〕〔LQA模板〕=本次新增。⊕=新增检查项</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>用法：Step 2 评估前与项目 adjudications.md 同读；源文档 docs/质量检查项清单.md（更新以 md 为准，本表由 scripts/gen_checklist_xlsx.py 重导）</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>规则来源代号（全表通用，〔〕标注）</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>代号</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>出处文档</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>0512 失分画像（优先级依据，源：LQE 报告评分卡）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>SKILL</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>SKILL.md（现行 skill 主文档；R 号=docs/LQE质量标准优化报告.html 的 R1-R30 整改项，上游分析=差距分析 GAP-06）</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>重复(不罚分)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>加权罚分</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>占比</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>projects/wwm/sg.txt（WWM 权威风格指南）</t>
+          <t>Mistranslation</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>783</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>85.6%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ADJ</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>projects/wwm/adjudications.md 0512 前旧段（历史 LQE 经验）</t>
+          <t>Terminology</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>docs/差距分析.md（GAP-01~08）</t>
+          <t>Company style</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>调研</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>docs/调研-行业标准证据简报.md</t>
+          <t>Unidiomatic</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>0512</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>0512 人工 LQE 报告·错误明细＋LQA Scorecard sheet（本次新证据）</t>
+          <t>Inconsistency</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>0.8%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>0512def</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>同报告 Error Definition sheet（客户权威错误定义表，含逐类三档严重度例）</t>
+          <t>其余 12 类</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>LQA</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>客户 LQA 译员评估模板（How to Fill / Score-for evaluator sheet，本次新证据）</t>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>915</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>41 个 Critical 构成：对联 26＋对联流对话 3＋玩法规则文本 7＋活动名/考勤 UI 5</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>0512 失分画像（优先级依据）</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>教训① 85% 失分来自 Mistranslation——重灾区是成组文本拆单句直译与规则文本语义错</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>重复(不罚分)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>加权罚分</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>占比</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>教训② 确定性类（Markup/Length/标点/拼写/漏多译）零错，pre-check 路线有效</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Mistranslation</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>783</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>85.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Terminology</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>9.8%</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>教训③ 下一批输入《玩法数据表_题目表_皇宫以外内容.xlsx》与对联块同型，最高危，必须成组评估</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Company style</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>2.8%</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>评估元规则（每条错误先过）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Unidiomatic</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>1.0%</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>来源</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Inconsistency</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>0.8%</t>
+          <t>三点法则</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>准确＋合规（SG/指令/术语）＋合语法→视为正确，偏好性改写不计错（至多 Neutral 建议）。防误报第一道闸</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>LQA模板（新增）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>其余 12 类</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>单一归属＋存疑取重</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>按归类决策表取最具体一类；Minor/Major 拿不准取 Major</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Skill 沿用</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>915</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>Word Choice 边界</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>意思错→Mistranslation；意思对但有更优词→Unidiomatic(Min) 或 Neutral</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>LQA模板（新增）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>41 个 Critical 构成：对联 26＋对联流对话 3＋玩法规则文本 7＋活动名/考勤 UI 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>教训① 85% 失分来自 Mistranslation——重灾区是成组文本拆单句直译与规则文本语义错</t>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>严重度三档锚</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Minor=可察觉不误导；Major=很可能误导玩家/损公信；Critical=投诉/法务/功能破坏/高曝光面</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Skill 沿用＋LQE报告定义表逐类细化</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>教训② 确定性类（Markup/Length/标点/拼写/漏多译）零错，pre-check 路线有效</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>计分与流程规则</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>教训③ 下一批输入《玩法数据表_题目表_皇宫以外内容.xlsx》与对联块同型，最高危，必须成组评估</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>重复错误</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>记录（Repeated=YES）不罚分，首次全额</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>LQE报告（新增）</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>34 条 rep 罚分=0</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>评估元规则（每条错误先过）</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>阈值分层</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>TEP/MTPE=98；润色/二审=99</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>LQE报告（新增）</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>客户错误定义表；profile.threshold 已支持</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>规则来源</t>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>严重度分值</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>0/1/5/10</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Skill 沿用（与 LQE 报告一致）</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>两份文档一致</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>三点法则</t>
+          <t>公式</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>准确＋合规（SG/指令/术语）＋合语法→视为正确，偏好性改写不计错（至多 Neutral 建议）。防误报第一道闸</t>
+          <t>score=1−Σ(加权罚分)/词数；词数口径=target-words</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>LQA How to Fill（新增）</t>
+          <t>Skill 沿用（与 LQE 报告完全一致）</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>0512 复算吻合（5,314 词）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>单一归属＋存疑取重</t>
+          <t>成组文本</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>按归类决策表取最具体一类；Minor/Major 拿不准取 Major</t>
+          <t>对联/题目/谜题按组评估：上下联对仗＋押韵＋题目-答案可配对；拆单句直译=组级 Critical</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>SKILL §归类决策规则←调研 §1.4 J2450 元规则（沿用）</t>
+          <t>LQE报告（新增）</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>对联块 26 Cri</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Word Choice 边界</t>
+          <t>文本类型判级倾向</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>意思错→Mistranslation；意思对但有更优词→Unidiomatic(Min) 或 Neutral</t>
+          <t>规则说明→错译默认 Cri；UI 短串→Unidiomatic/style 主导；诗句 banner→Company style 重写权</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>LQA 模板明文（新增）</t>
+          <t>LQE报告（新增）</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>0512 判级分布</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>严重度三档锚</t>
+          <t>报告解析</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Minor=可察觉不误导；Major=很可能误导玩家/损公信；Critical=投诉/法务/功能破坏/高曝光面</t>
+          <t>corrected 列可为 #N/A（审校未给改稿）；Repeated 列 YES/NO</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>SKILL 严重度判定（沿用）＋0512def 逐类细化</t>
+          <t>LQE报告（新增）</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>实表格式</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>计分与流程规则</t>
+          <t>待落地变更</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>规则</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>变更</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>规则来源</t>
+          <t>目标</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>证据</t>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>重复错误</t>
-        </is>
+      <c r="A43" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>记录（Repeated=YES）不罚分，首次全额</t>
+          <t>重复错误去重计分（N4）</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>0512 Scorecard 实证（新增）；问题背景=GAP-07</t>
+          <t>scripts/lqe_calc.py</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>34 条 rep 罚分=0</t>
+          <t>待 go</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>阈值分层</t>
-        </is>
+      <c r="A44" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>TEP/MTPE=98；润色/二审=99</t>
+          <t>拼音残留（N1）＋同源异译（N2）</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>数值=0512def（新增）；分层概念上游=调研 §3 DQF</t>
+          <t>scripts/lqe_io.py pre-check</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>客户 Error Definition 表；profile.threshold 已支持</t>
+          <t>待 go</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>严重度分值</t>
-        </is>
+      <c r="A45" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>0/1/5/10（客户=LISA 制，非 MQM 25）——GAP-03 的 MQM 调参不采</t>
+          <t>罗马数字 custom（N3）</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>SKILL 沿用；与 0512def 一致</t>
+          <t>projects/wwm/checks.json</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>两报告一致</t>
+          <t>待 go</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
+      <c r="A46" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>score=1−Σ(加权罚分)/词数；词数口径=target-words</t>
+          <t>0512 术语/风格裁决注入</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>SKILL 沿用；与 0512def 完全一致</t>
+          <t>projects/wwm/adjudications.md</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>0512 复算吻合（5,314 词）</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>成组文本</t>
-        </is>
+      <c r="A47" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>对联/题目/谜题按组评估：上下联对仗＋押韵＋题目-答案可配对；拆单句直译=组级 Critical</t>
+          <t>Step 2 评估提示引用本清单</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>0512 错误明细（全新）</t>
+          <t>SKILL.md</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>对联块 26 Cri</t>
+          <t>待 go</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>内容桶倾向</t>
-        </is>
+      <c r="A48" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>规则说明→错译默认 Cri；UI 短串→Unidiomatic/style 主导；诗句 banner→Company style 重写权</t>
+          <t>题目表/对联输入带组上下文</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>概念=调研 §2.3/GAP-05；具体倾向=0512（新增）</t>
+          <t>lqe_io.py read / Step 2 流程</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>0512 判级分布</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>报告解析</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>corrected 列可为 #N/A（审校未给改稿）；Repeated 列 YES/NO</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>0512 实表（新增）</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>r129 等</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>待落地变更</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>目标</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>重复错误去重计分（N4）</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>scripts/lqe_calc.py</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>待 go</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>拼音残留（N1）＋同源异译（N2）</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>scripts/lqe_io.py pre-check</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>待 go</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>罗马数字 custom（N3）</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>projects/wwm/checks.json</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>待 go</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>0512 术语/风格裁决注入</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>projects/wwm/adjudications.md</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Step 2 评估提示引用本清单</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>SKILL.md</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>待 go</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>题目表/对联输入带组上下文</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>lqe_io.py read / Step 2 流程</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>待 go（下批题目表前急需）</t>
         </is>
@@ -1339,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1347,10 +1239,9 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1381,20 +1272,15 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>规则来源</t>
+          <t>评估关注点</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>评估关注点</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>落地</t>
         </is>
@@ -1428,20 +1314,15 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>SKILL Step1.5 初版</t>
+          <t>指令允许保留项除外</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>指令允许保留项除外</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1475,20 +1356,15 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>SKILL Step1.5</t>
+          <t>口径与词数基准联动（source-chars 时仍计分）</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>口径与词数基准联动（source-chars 时仍计分）</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1522,20 +1398,15 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>SKILL 初版＋SG 标点</t>
+          <t>项目可关（nrc-en 已关）</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>项目可关（nrc-en 已关）</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1569,20 +1440,15 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>SKILL 初版＋SG Markup</t>
+          <t>相对位置也须一致，非仅数量</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>相对位置也须一致，非仅数量</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1616,20 +1482,15 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>SKILL 初版＋SG Markup</t>
+          <t>0512 实证：「{}天后领取{}」丢一个占位符被人工判 Mistranslation Critical——占位符错按客户口径是最重级〔LQE报告〕</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>0512 实证：「{}天后领取{}」丢一个占位符被人工判 Mistranslation Critical——占位符错按客户口径是最重级〔0512〕</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1663,20 +1524,15 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>SKILL R1 整改←GAP-06</t>
+          <t>命名/带索引占位符允许重排</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>命名/带索引占位符允许重排</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1710,16 +1566,11 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>SKILL 初版＋SG</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
+          <t>Skill 沿用</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1753,20 +1604,15 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>SKILL R6 整改←GAP-06</t>
+          <t>仅源含阿拉伯数字触发；中文数字不误报；语境误报可移除</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>仅源含阿拉伯数字触发；中文数字不误报；语境误报可移除</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1800,20 +1646,15 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>max-length=SKILL R3←GAP-06；1.5× 回退=初版</t>
+          <t>max-length 列优先；无列时仅非 CJK 源回退</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>max-length 列优先；无列时仅非 CJK 源回退</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1847,16 +1688,11 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>SKILL 初版＋SG 数字</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
+          <t>Skill 沿用</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1890,16 +1726,11 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>SKILL R5 整改←GAP-06</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
+          <t>Skill 沿用</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1933,16 +1764,11 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>SKILL R5 整改＋SG 半角标点</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
+          <t>Skill 沿用</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -1976,20 +1802,15 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>现行沿用</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>SKILL 初版；TB:status 机制=项目档案</t>
+          <t>[TB:status]：Approved 硬判；New/WorkingTB 语境甄别；泛词命中≠错误</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>[TB:status]：Approved 硬判；New/WorkingTB 语境甄别；泛词命中≠错误〔ADJ〕</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>内置</t>
         </is>
@@ -2023,20 +1844,15 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>⊕新增</t>
+          <t>⊕新增·LQE报告</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>0512 全新发现</t>
+          <t>target 含 2+ 连续拼音音节大写词且不在官方拼音白名单（Kaifeng/Qinghe/Jianghu/Fu Shen/Xuanyu…）。实证：画卯→Mark Mao、平安→Ping'an 均 Cri。半确定：regex 初筛＋AI 复核</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>target 含 2+ 连续拼音音节大写词且不在官方拼音白名单（Kaifeng/Qinghe/Jianghu/Fu Shen/Xuanyu…）。0512：画卯→Mark Mao、平安→Ping'an 均 Cri。半确定：regex 初筛＋AI 复核</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>pre-check 待落地</t>
         </is>
@@ -2070,20 +1886,15 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>⊕新增</t>
+          <t>⊕新增·LQE报告</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>GAP-06「文件内一致性」首次落清单；0512 实证支持</t>
+          <t>文件内相同 source 不同 target；反向（相同 target 不同 source）一并报（报告 Inconsistency 实证的可机检子集）</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>文件内相同 source 不同 target；反向（相同 target 不同 source）一并报</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>pre-check 待落地</t>
         </is>
@@ -2117,20 +1928,15 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>⊕新增</t>
+          <t>⊕新增·LQE报告</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>0512 改稿风格</t>
+          <t>序号/卷号用 Unicode Ⅰ Ⅱ Ⅲ，非 ASCII I/II/III（实证：其一→Ⅰ、Volume Ⅱ）</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>序号/卷号用 Unicode Ⅰ Ⅱ Ⅲ，非 ASCII I/II/III（0512：其一→Ⅰ、Volume Ⅱ）</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>wwm checks.json 待落地</t>
         </is>
@@ -2164,20 +1970,15 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>⊕新增</t>
+          <t>⊕新增·LQE报告</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>问题=GAP-07 死列；策略=0512 实证落定</t>
+          <t>同源＋同译＋同错仅首次计分，其余标 Repeated=YES 不罚分（实证：34 条 rep 罚分=0）</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>同源＋同译＋同错仅首次计分，其余标 Repeated=YES 不罚分（0512：34 条 rep 罚分=0）</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>lqe_calc.py 待落地</t>
         </is>
@@ -2209,7 +2010,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>子类体系/权重/强制 Major/严重度 0-1-5-10 全部沿用〔SKILL §LQE错误分类；七父维度=GAP-01/02 整改〕；「严重度梯度」列统一取自〔0512def〕；关注点逐条〔〕标来源</t>
+          <t>子类体系/权重/强制 Major/严重度 0-1-5-10 全部沿用〔Skill〕，与 LQE 报告客户错误定义表逐项核对一致；「严重度梯度」列统一取自 LQE 报告·客户错误定义表；关注点逐条〔〕标来源</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2042,12 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>评估关注点（〔〕=规则来源）</t>
+          <t>评估关注点（〔〕=来源）</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>严重度梯度（源:0512def）</t>
+          <t>严重度梯度（源:LQE报告定义表）</t>
         </is>
       </c>
     </row>
@@ -2276,11 +2077,11 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>• 专名↔通名双向误判：拼音残留（画卯→Roll Call，×Mark Mao；平安→Peace，×Ping'an）；通名实体化幻觉（年年≠Niannian；岁月长安≠Chang'an；紫色团花=purple flower，×Epic Flower）〔0512〕
-• 玩法规则文本逐条核：数值/上限/门槛（铜筹折算上限2000）、阶段流程序、机制词（多轮循环=Round-robin，×Rotating）、奖励归属与返还条件——客户一律 Critical〔0512〕
-• 操作指引动作语义：技能效果的对象与方式（复原巨石使其停下≠restore…to a halt；招式=any attack，×a Move）〔0512〕
-• 价格/概率语义词不可丢：折扣价、有机会获得（Cri 例：源「有机会获得[68金币]」译 contains）；回復≠receive〔0512＋0512def〕
-• 升 Cri 信号：误导玩家决策的规则文/题目-答案失配/占位符语义错位/经济敏感〔0512〕</t>
+          <t>• 专名↔通名双向误判：拼音残留（画卯→Roll Call，×Mark Mao；平安→Peace，×Ping'an）；通名实体化幻觉（年年≠Niannian；岁月长安≠Chang'an；紫色团花=purple flower，×Epic Flower）〔LQE报告〕
+• 玩法规则文本逐条核：数值/上限/门槛（铜筹折算上限2000）、阶段流程序、机制词（多轮循环=Round-robin，×Rotating）、奖励归属与返还条件——客户一律 Critical〔LQE报告〕
+• 操作指引动作语义：技能效果的对象与方式（复原巨石使其停下≠restore…to a halt；招式=any attack，×a Move）〔LQE报告〕
+• 价格/概率语义词不可丢：折扣价、有机会获得（Cri 例：源「有机会获得[68金币]」译 contains）；回復≠receive〔LQE报告〕
+• 升 Cri 信号：误导玩家决策的规则文/题目-答案失配/占位符语义错位/经济敏感〔LQE报告〕</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -2315,8 +2116,8 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>• 限定词清点：任意/1次/仅/同时/最高/每（0512 近失：a Sword Trial 丢「任意」）〔0512〕
-• 进度/资格条件（充值/达标/解锁）丢失即 Cri〔0512def〕</t>
+          <t>• 限定词清点：任意/1次/仅/同时/最高/每（近失例：a Sword Trial 丢「任意」）〔LQE报告〕
+• 进度/资格条件（充值/达标/解锁）丢失即 Cri〔LQE报告〕</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2351,8 +2152,8 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>• 贴源过译与偏离区分〔0512def〕
-• 勿引入不存在的玩法元素（单体伤害→all enemies）〔0512def〕</t>
+          <t>• 贴源过译与偏离区分〔LQE报告〕
+• 勿引入不存在的玩法元素（单体伤害→all enemies）〔LQE报告〕</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2387,8 +2188,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>• 拼音输出≠已翻译——按 Mistranslation Cri 处理（N1）〔0512〕
-• 英文源原样复制也算未译（不止中文残留）〔GAP-06 未译扩展〕</t>
+          <t>• 拼音输出≠已翻译——按 Mistranslation Cri 处理（N1）〔LQE报告〕</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2423,13 +2223,13 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>• 活动/玩法/界面入口名逐字对官方库与已上线译名：皇宫寻宝=Imperial Palace Treasure Hunt（自创=Maj）；御前练兵=Imperial Drill〔0512〕
-• 成对称号体系成对取：新锐|新兵=Recruit／老将|老兵=Veteran（×New Edge/Old General）〔0512〕
-• 人名代号查角色档：青=Halcyon（×Qing 直拼）〔0512〕
-• 同物跨段同名：手札统一 Journal（×Note）〔0512〕
-• 过度术语化=错：通名勿造专名（异色灵蝶=strangely colored butterflies，×Spectral Butterfly）〔0512〕
-• 系列名格式：赋神·乘桴归梦=Fu Shen - Rippling Dream（系列前缀保留〔0512〕；·→" - "=SG 既有规则〔SG〕）
-• 强制定译 19 条见 projects/wwm/adjudications.md《0512 裁决》〔0512〕；泛词命中按语境甄别〔ADJ 沿用〕</t>
+          <t>• 活动/玩法/界面入口名逐字对官方库与已上线译名：皇宫寻宝=Imperial Palace Treasure Hunt（自创=Maj）；御前练兵=Imperial Drill〔LQE报告〕
+• 成对称号体系成对取：新锐|新兵=Recruit／老将|老兵=Veteran（×New Edge/Old General）〔LQE报告〕
+• 人名代号查角色档：青=Halcyon（×Qing 直拼）〔LQE报告〕
+• 同物跨段同名：手札统一 Journal（×Note）〔LQE报告〕
+• 过度术语化=错：通名勿造专名（异色灵蝶=strangely colored butterflies，×Spectral Butterfly）〔LQE报告〕
+• 系列名格式：赋神·乘桴归梦=Fu Shen - Rippling Dream（系列前缀保留；·→" - "）〔LQE报告＋Skill〕
+• 强制定译 19 条见 projects/wwm/adjudications.md《0512 裁决》〔LQE报告〕；泛词命中按语境甄别〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -2464,9 +2264,9 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>• 平行句族统一句型：任务/成就列表同模板（Complete any X once with a Veteran/Recruit 族）〔0512〕
-• 任务名引用格式统一（Lost Chapter quest: X）〔0512〕
-• 涉术语表词条的冲突归 Terminology，其余归此〔SKILL 归类决策表沿用〕</t>
+          <t>• 平行句族统一句型：任务/成就列表同模板（Complete any X once with a Veteran/Recruit 族）〔LQE报告〕
+• 任务名引用格式统一（Lost Chapter quest: X）〔LQE报告〕
+• 涉术语表词条的冲突归 Terminology，其余归此〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2501,8 +2301,8 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>• 主谓一致/时态/冠词〔0512def/LQA 通则〕
-• 占位符邻接可数名词用「{} day(s)」型复数〔0512〕</t>
+          <t>• 主谓一致/时态/冠词〔LQE报告〕
+• 占位符邻接可数名词用「{} day(s)」型复数〔LQE报告〕</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -2537,8 +2337,8 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>• 半角标点、对齐源标点（pre-check/custom 已盖大半）〔SG＋SKILL 沿用〕
-• 长句逗号缺失影响可读性〔LQA〕</t>
+          <t>• 半角标点、对齐源标点（pre-check 已盖大半）〔Skill 沿用〕
+• 长句逗号缺失影响可读性〔LQA模板〕</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2573,8 +2373,8 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>• Equipments/Acheive/Entrence 型错拼〔0512def〕
-• 易混词 accept/except、then/than、your/you're=Maj〔0512def〕</t>
+          <t>• Equipments/Acheive/Entrence 型错拼〔LQE报告〕
+• 易混词 accept/except、then/than、your/you're=Maj〔LQE报告〕</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -2609,11 +2409,11 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>• 句中通名小写：accept a quest / the treasure（×句中 Accept a Quest）〔0512；Title/Sentence Mode 本体=SG 沿用〕
-• 序号/卷号 Unicode 罗马数字（N3）〔0512〕
-• 括号体系：设施/可放置物名 [Stove]（×「」原样、×#Y"X"#E 引号式）〔0512〕
-• 诗句/banner 有押韵节奏重写权（九天阊阖联→bold/gold 韵对）；过度直译判此类〔0512〕
-• 禁古英语/网络俚语/UI 语气进剧情〔SG 沿用〕；SG 明文违反才归此，无明文归 Unidiomatic〔SKILL 归类决策表沿用〕</t>
+          <t>• 句中通名小写：accept a quest / the treasure（×句中 Accept a Quest）〔LQE报告；Title/Sentence Mode 本体=Skill 沿用〕
+• 序号/卷号 Unicode 罗马数字（N3）〔LQE报告〕
+• 括号体系：设施/可放置物名 [Stove]（×「」原样、×#Y"X"#E 引号式）〔LQE报告〕
+• 诗句/banner 有押韵节奏重写权（九天阊阖联→bold/gold 韵对）；过度直译判此类〔LQE报告〕
+• 禁古英语/网络俚语/UI 语气进剧情；SG 明文违反才归此，无明文归 Unidiomatic〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -2648,9 +2448,9 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>• UI 短句自然化模板：Continue Completing &lt;X&gt;→Continue completing the X quest（去尖括号＋补通名 quest＋句子化大小写）——0512 同一模式重复 12 次〔0512；非代码禁 &lt;&gt; 旧规=ADJ〕
-• 直译腔标志：Warm Tips / Successfully Claimed 型〔0512def〕
-• 三档标尺：母语者难懂／直译但可懂／好文笔——仅前两档计错〔LQA Naturalness，新增〕</t>
+          <t>• UI 短句自然化模板：Continue Completing &lt;X&gt;→Continue completing the X quest（去尖括号＋补通名 quest＋句子化大小写）——同一模式重复 12 次〔LQE报告〕
+• 直译腔标志：Warm Tips / Successfully Claimed 型〔LQE报告〕
+• 三档标尺：母语者难懂／直译但可懂／好文笔——仅前两档计错〔LQA模板，新增〕</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -2685,8 +2485,8 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>• 日期防歧义拼写月份（6/5/2023→May 6, 2023）〔0512def〕
-• 货币符号与币种一致〔0512def〕</t>
+          <t>• 日期防歧义拼写月份（6/5/2023→May 6, 2023）〔LQE报告〕
+• 货币符号与币种一致〔LQE报告〕</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -2721,8 +2521,8 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>• 源文化梗错置目标受众（520、圣诞吃苹果）〔0512def〕
-• 冒犯/涉政/禁忌=Cri〔0512def〕</t>
+          <t>• 源文化梗错置目标受众（520、圣诞吃苹果）〔LQE报告〕
+• 冒犯/涉政/禁忌=Cri〔LQE报告〕</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -2757,8 +2557,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>• 语域/世界观口吻（仙侠敬语→现代俚语）〔SKILL←GAP-01 整改沿用〕
-• 准确但不合受众期待〔SKILL 沿用〕</t>
+          <t>• 语域/世界观口吻（仙侠敬语→现代俚语）；准确但不合受众期待〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2793,7 +2592,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>• 色标相对位置、{} 数量与顺序、\n 保留〔SKILL＋SG 沿用〕</t>
+          <t>• 色标相对位置、{} 数量与顺序、\n 保留〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2828,7 +2627,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>• max-length 列优先；超长截断风险〔SKILL R3←GAP-06〕</t>
+          <t>• max-length 列优先；超长截断风险〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2863,7 +2662,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>• 兜底；先过单一归属表再落此〔SKILL 沿用〕</t>
+          <t>• 兜底；先过单一归属表再落此〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">

--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>LQA模板（新增）</t>
+          <t>边界=LQA模板明文；落到 Unidiomatic/Neutral=本清单适配（skill 无 Word Choice 类）</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Skill 沿用＋LQE报告定义表逐类细化</t>
+          <t>Skill＋LQE报告定义表＋LQA模板三处定义的合成转述，非逐字</t>
         </is>
       </c>
     </row>

--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概览与计分规则" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="确定性pre-check项" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="确定性检查项" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI评估项17子类" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -474,13 +474,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -496,232 +496,192 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>更新 2026-06-11。参考仅三份（来源标注用〔〕）：</t>
+          <t>更新日期：2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>〔Skill〕现行 skill（SKILL.md：pre-check 13 项、17 子类、权重/强制 Major、公式、归类决策、严重度判定）</t>
+          <t>参考文件（共三份）：</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>〔LQE报告〕0512《【AI】【英】globaltrunk【0511新增】_LQE Report.xlsx》＝WWM 中→英 AI 译文人工 LQE（5,314 词，82.78 FAIL，计分错误 101＋重复 34；含错误明细/评分卡/客户错误定义表）</t>
+          <t>〔Skill〕现行评估体系 SKILL.md：确定性检查 13 项、错误子类 17 项、权重与强制严重度、评分公式、归类规则</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>〔LQA模板〕《LQA template to evaluate current cooperating translators.xlsx》（客户译员评估模板）</t>
+          <t>〔LQE报告〕《【AI】【英】0512【globaltrunk】【0511新增】_LQE Report.xlsx》：客户对 AI 译文（中→英）的人工质量评估报告，含 Error Severity、Error Definition（错误定义表）、LQA Scorecard（评分卡及 135 条错误明细）三个工作表</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>〔Skill〕=沿用现行体系；〔LQE报告〕〔LQA模板〕=本次新增。⊕=新增检查项</t>
+          <t>〔LQA模板〕《LQA template to evaluate current cooperating translators.xlsx》：客户用于评估合作译员的 LQA 模板</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>用法：Step 2 评估前与项目 adjudications.md 同读；源文档 docs/质量检查项清单.md（更新以 md 为准，本表由 scripts/gen_checklist_xlsx.py 重导）</t>
+          <t>标注约定：〔Skill〕＝沿用现行体系；〔LQE报告〕〔LQA模板〕＝本次依据该文件新增；“第 N 段”指 LQE 报告错误明细中的 Segment 编号，便于核对原文；凡属归纳推断处均注明“归纳”，不作为客户明文规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>报告基础数据：总词数 5,314；总分 82.78，低于阈值 98，判定 FAIL；计分错误 101 条（Minor 25、Major 35、Critical 41），另有重复标记错误 34 条（不计罚分）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>0512 失分画像（优先级依据，源：LQE 报告评分卡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>源文档：docs/质量检查项清单.md（内容更新以该文件为准，本表由 scripts/gen_checklist_xlsx.py 重新导出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>错误分布（来源：LQE 报告评分卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>重复(不罚分)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>重复标记</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>加权罚分</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>占比</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Mistranslation</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>783</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>85.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Terminology</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>9.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Company style</t>
+          <t>Mistranslation</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>25.5</v>
+        <v>783</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>85.6%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Unidiomatic</t>
+          <t>Terminology</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Inconsistency</t>
+          <t>Company style</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7.5</v>
+        <v>25.5</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>其余 12 类</t>
+          <t>Unidiomatic</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>0</v>
@@ -730,493 +690,547 @@
         <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Inconsistency</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>其余 12 类</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C20" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D20" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E20" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F20" s="5" t="n">
         <v>915</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>41 个 Critical 构成：对联 26＋对联流对话 3＋玩法规则文本 7＋活动名/考勤 UI 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>教训① 85% 失分来自 Mistranslation——重灾区是成组文本拆单句直译与规则文本语义错</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>教训② 确定性类（Markup/Length/标点/拼写/漏多译）零错，pre-check 路线有效</t>
+          <t>41 条 Critical 的内容构成（本清单依据错误明细整理）：成对祝词短句 26 条（第 47–75 段；修订译文呈两两押韵对应，如 Door/Floor、Grows/Flows）；同流程对话选项 3 条（第 42–46 段）；玩法规则说明 7 条（第 256–265 段）；活动名称及签到界面文本 5 条</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>教训③ 下一批输入《玩法数据表_题目表_皇宫以外内容.xlsx》与对联块同型，最高危，必须成组评估</t>
+          <t>主要结论 1：加权罚分的 85.6% 来自 Mistranslation，集中于成对短句的逐句直译与规则说明文本的语义错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>主要结论 2：Markup、Length、Punctuation、Spelling、Omission、Addition、Untranslated 等可由确定性检查覆盖的类别，本报告中均为零错误，现行 pre-check 机制有效</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>评估元规则（每条错误先过）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>主要结论 3：待评估文件《玩法数据表_题目表_皇宫以外内容.xlsx》与本次 Critical 集中的题目类文本属同类内容，预计存在同类风险（归纳推断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>通用评估原则（评估每条错误前先行核对）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>原则</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>三点法则</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>准确＋合规（SG/指令/术语）＋合语法→视为正确，偏好性改写不计错（至多 Neutral 建议）。防误报第一道闸</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>LQA模板（新增）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>单一归属＋存疑取重</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>按归类决策表取最具体一类；Minor/Major 拿不准取 Major</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Skill 沿用</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Word Choice 边界</t>
+          <t>三点法则</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>意思错→Mistranslation；意思对但有更优词→Unidiomatic(Min) 或 Neutral</t>
+          <t>译文同时满足准确（核心含义保留）、合规（符合风格指南、项目指令与术语表）、合乎语法三项，即视为正确；偏好性改写不计为错误，至多记 Neutral 建议</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>边界=LQA模板明文；落到 Unidiomatic/Neutral=本清单适配（skill 无 Word Choice 类）</t>
+          <t>LQA模板原文（新增）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>严重度三档锚</t>
+          <t>单一归属与从重判定</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Minor=可察觉不误导；Major=很可能误导玩家/损公信；Critical=投诉/法务/功能破坏/高曝光面</t>
+          <t>每条错误只归入一个类别，取最具体的一类；严重度在 Minor 与 Major 之间无法确定时，判 Major</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Skill＋LQE报告定义表＋LQA模板三处定义的合成转述，非逐字</t>
+          <t>Skill 沿用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Word Choice 判定边界</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>用词导致含义错误的，归 Mistranslation；含义正确但存在更优用词的，归 Unidiomatic（Minor）或记 Neutral。前半句为 LQA 模板原文；归入 Unidiomatic/Neutral 系本清单适配（现行体系无 Word Choice 类别）</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>LQA模板＋本清单适配</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>严重度三级判定基准</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Minor＝可察觉但不致误导；Major＝很可能误导玩家或损害可信度；Critical＝可能引起投诉、法律风险、功能破坏或出现在高可见位置。系对三处定义的综合转述，非逐字引用</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Skill＋LQE报告定义表＋LQA模板综合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>计分与流程规则</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>规则</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>证据</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>重复错误</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>记录（Repeated=YES）不罚分，首次全额</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>LQE报告（新增）</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>34 条 rep 罚分=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>阈值分层</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>TEP/MTPE=98；润色/二审=99</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>LQE报告（新增）</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>客户错误定义表；profile.threshold 已支持</t>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>核验依据</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>严重度分值</t>
+          <t>重复错误</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>0/1/5/10</t>
+          <t>重复错误予以记录（Repeated=YES）但不计罚分，仅首次计分</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Skill 沿用（与 LQE 报告一致）</t>
+          <t>LQE报告（新增）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>两份文档一致</t>
+          <t>评分卡复核：罚分 610 恰等于非重复错误之和（25×1＋35×5＋41×10），34 条重复错误未计入</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>公式</t>
+          <t>阈值分级</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>score=1−Σ(加权罚分)/词数；词数口径=target-words</t>
+          <t>TEP、MTPE 阈值 98；润色、二审阈值 99</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Skill 沿用（与 LQE 报告完全一致）</t>
+          <t>LQE报告（新增）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>0512 复算吻合（5,314 词）</t>
+          <t>错误定义表原文（0.98／0.99）；现行 profile.threshold 参数已支持配置</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>成组文本</t>
+          <t>严重度分值</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>对联/题目/谜题按组评估：上下联对仗＋押韵＋题目-答案可配对；拆单句直译=组级 Critical</t>
+          <t>Neutral 0／Minor 1／Major 5／Critical 10</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>LQE报告（新增）</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>对联块 26 Cri</t>
+          <t>与 LQE 报告 Error Severity 工作表一致</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>文本类型判级倾向</t>
+          <t>评分公式</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>规则说明→错译默认 Cri；UI 短串→Unidiomatic/style 主导；诗句 banner→Company style 重写权</t>
+          <t>得分＝1－加权罚分合计÷词数</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>LQE报告（新增）</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>0512 判级分布</t>
+          <t>错误定义表原文 Score = 1 - Penalty total/Wordcount；按报告数据复核（1－915÷5314＝82.78）一致</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>报告解析</t>
+          <t>成组文本评估</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>corrected 列可为 #N/A（审校未给改稿）；Repeated 列 YES/NO</t>
+          <t>对联、题目、谜题类文本按组评估：上下联对仗与押韵、题目与答案的对应关系须保持；逐句独立直译将破坏成组结构</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
+          <t>本清单依据 LQE 报告归纳（新增）</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>26 条成对短句 Critical 的修订稿呈两两押韵模式；报告未附判定理由，成因系归纳推断</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>文本类型与判级倾向</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>规则说明类错译普遍判 Critical；界面短句问题多归 Unidiomatic 或 Company style；诗句宣传语按风格改写要求评估</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>本清单依据 LQE 报告判级分布归纳（新增）</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>规则说明类错译 7 条均为 Critical；界面短句 12 条均为 Unidiomatic Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>报告格式解析</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>修订列可为 #N/A（审校未提供修订稿）；重复列取值 YES/NO</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
           <t>LQE报告（新增）</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>实表格式</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>待落地变更</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>目标</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>第 259 段修订列为 #N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>后续实施事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>涉及文件</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>重复错误去重计分（N4）</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>scripts/lqe_calc.py</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>待 go</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>拼音残留（N1）＋同源异译（N2）</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>scripts/lqe_io.py pre-check</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>待 go</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>罗马数字 custom（N3）</t>
+          <t>重复错误计分规则（N4）</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>projects/wwm/checks.json</t>
+          <t>scripts/lqe_calc.py</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>待 go</t>
+          <t>待批准</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>0512 术语/风格裁决注入</t>
+          <t>拼音残留检查（N1）、同源异译检查（N2）</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>projects/wwm/adjudications.md</t>
+          <t>scripts/lqe_io.py</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>待批准</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Step 2 评估提示引用本清单</t>
+          <t>罗马数字检查（N3）</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>SKILL.md</t>
+          <t>projects/wwm/checks.json</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>待 go</t>
+          <t>待批准</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>0512 报告术语与风格裁决归档</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>projects/wwm/adjudications.md</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>已完成（2026-06-11）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>评估流程引用本清单</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>SKILL.md</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>待批准</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>题目表/对联输入带组上下文</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>lqe_io.py read / Step 2 流程</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>待 go（下批题目表前急需）</t>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>题目类文本按组送评（同组段落合并提供评估上下文）</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py 及评估流程</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>待批准；建议在下一批题目表评估前完成</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1250,12 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="72" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1252,12 +1266,12 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>键/ID</t>
+          <t>键/编号</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>检查项</t>
+          <t>检查内容</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -1282,7 +1296,7 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>落地</t>
+          <t>实施位置</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1313,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>target 含中文</t>
+          <t>译文残留中文</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1319,7 +1333,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>指令允许保留项除外</t>
+          <t>项目指令允许保留的内容除外</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -1341,7 +1355,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>空译文</t>
+          <t>译文为空</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1361,7 +1375,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>口径与词数基准联动（source-chars 时仍计分）</t>
+          <t>与词数统计方式联动（source-chars 模式下仍计分）</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1383,7 +1397,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>破折号 —</t>
+          <t>破折号“—”</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1403,7 +1417,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>项目可关（nrc-en 已关）</t>
+          <t>可按项目配置关闭</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -1425,7 +1439,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>#G/#C/#Y…#E 配对</t>
+          <t>颜色标签 #G/#C/#Y…#E 配对</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1445,7 +1459,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>相对位置也须一致，非仅数量</t>
+          <t>相对位置须一致，不限于数量</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -1467,7 +1481,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>{} / %s 缺失多余</t>
+          <t>占位符 {}/%s 缺失或多余</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1487,7 +1501,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>0512 实证：「{}天后领取{}」丢一个占位符被人工判 Mistranslation Critical——占位符错按客户口径是最重级〔LQE报告〕</t>
+          <t>LQE 报告中“{}天后领取{}”译文缺失一个占位符，被评为 Mistranslation Critical（第 107 段）〔LQE报告〕</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1529,7 +1543,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>命名/带索引占位符允许重排</t>
+          <t>命名式或带索引的占位符允许重排</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1551,7 +1565,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>\n 数量不匹配</t>
+          <t>换行符 \n 数量不一致</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1589,7 +1603,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>数值漏译/改值</t>
+          <t>数值缺失或改动</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1609,7 +1623,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>仅源含阿拉伯数字触发；中文数字不误报；语境误报可移除</t>
+          <t>仅当源文含阿拉伯数字时触发；中文数字不误报；上下文确认后可移除误报</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1631,7 +1645,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>max-length / 1.5× 超长</t>
+          <t>超出长度限制</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1651,7 +1665,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>max-length 列优先；无列时仅非 CJK 源回退</t>
+          <t>优先使用 max-length 列；无该列时按 1.5 倍源文长度回退（仅非中日韩源文）</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1711,7 +1725,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>首尾空白/双空格</t>
+          <t>首尾空格、连续空格</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1749,7 +1763,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>EN 译文全角标点</t>
+          <t>英文译文中的全角标点</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1787,7 +1801,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>术语命中缺译</t>
+          <t>术语表命中但译文未采用</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1807,7 +1821,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>[TB:status]：Approved 硬判；New/WorkingTB 语境甄别；泛词命中≠错误</t>
+          <t>按术语状态区分：Approved 直接判错；New/WorkingTB 结合语境判断；通用词汇命中不等于错误</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1844,17 +1858,17 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>⊕新增·LQE报告</t>
+          <t>新增·LQE报告</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>target 含 2+ 连续拼音音节大写词且不在官方拼音白名单（Kaifeng/Qinghe/Jianghu/Fu Shen/Xuanyu…）。实证：画卯→Mark Mao、平安→Ping'an 均 Cri。半确定：regex 初筛＋AI 复核</t>
+          <t>译文中出现两个以上连续拼音音节构成的词，且不在官方保留拼音名单内（报告修订稿保留 Kaifeng、Qinghe、Jianghu、Fu Shen 等）。报告实例：“画卯”译为 Mark Mao（第 105 段）、“平安”译为 Ping'an（第 54 段），均评为 Critical。属半确定性检查：正则初筛后须人工或 AI 复核</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>pre-check 待落地</t>
+          <t>scripts/lqe_io.py（待批准）</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1885,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>同源异译</t>
+          <t>同文件内同源异译</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1886,17 +1900,17 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>⊕新增·LQE报告</t>
+          <t>新增·LQE报告</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>文件内相同 source 不同 target；反向（相同 target 不同 source）一并报（报告 Inconsistency 实证的可机检子集）</t>
+          <t>同一文件内相同源文对应不同译文；以及相同译文对应不同源文。系报告 Inconsistency 类错误（第 82–94 段）中可程序化检出的子集</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>pre-check 待落地</t>
+          <t>scripts/lqe_io.py（待批准）</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1927,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>罗马数字风格</t>
+          <t>序号用罗马数字字符</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1928,17 +1942,17 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>⊕新增·LQE报告</t>
+          <t>新增·LQE报告</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>序号/卷号用 Unicode Ⅰ Ⅱ Ⅲ，非 ASCII I/II/III（实证：其一→Ⅰ、Volume Ⅱ）</t>
+          <t>序号、卷号应使用 Unicode 罗马数字（Ⅰ Ⅱ Ⅲ），不使用 ASCII 字母拼写。报告实例：“其一”修订为“Ⅰ”（第 194 段）、“卷二”修订为“Volume Ⅱ”（第 268 段）</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>wwm checks.json 待落地</t>
+          <t>projects/wwm/checks.json（待批准）</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1969,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>重复错误去重计分</t>
+          <t>重复错误计分规则</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1970,17 +1984,17 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>⊕新增·LQE报告</t>
+          <t>新增·LQE报告</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>同源＋同译＋同错仅首次计分，其余标 Repeated=YES 不罚分（实证：34 条 rep 罚分=0）</t>
+          <t>重复出现的同一错误仅首次计罚分，其余标记 Repeated 不计分。依据：报告 34 条重复标记错误经评分卡复核均未计入罚分。重复判定条件（相同源文、相同译文、相同错误）系依据报告数据归纳，报告未明文定义</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>lqe_calc.py 待落地</t>
+          <t>scripts/lqe_calc.py（待批准）</t>
         </is>
       </c>
     </row>
@@ -1998,26 +2012,26 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="90" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="92" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>子类体系/权重/强制 Major/严重度 0-1-5-10 全部沿用〔Skill〕，与 LQE 报告客户错误定义表逐项核对一致；「严重度梯度」列统一取自 LQE 报告·客户错误定义表；关注点逐条〔〕标来源</t>
+          <t>子类体系、权重、强制 Major、严重度分值（0/1/5/10）全部沿用〔Skill〕，并经与 LQE 报告错误定义表逐项核对一致；“严重度分级”列统一取自 LQE 报告错误定义表；关注点逐条以〔〕标注来源，“第 N 段”为报告错误明细 Segment 编号</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>父维度</t>
+          <t>上级维度</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -2037,17 +2051,17 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>0512 计分</t>
+          <t>本次计分</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>评估关注点（〔〕=来源）</t>
+          <t>评估关注点（〔〕＝来源；“第 N 段”＝报告 Segment 编号）</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>严重度梯度（源:LQE报告定义表）</t>
+          <t>严重度分级（来源：LQE 报告错误定义表）</t>
         </is>
       </c>
     </row>
@@ -2072,21 +2086,21 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Min2·Maj22(+8rep)·Cri41(+5rep)＝最大失分源</t>
+          <t>Minor 2、Major 22（另重复 8）、Critical 41（另重复 5）；最大罚分来源</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>• 专名↔通名双向误判：拼音残留（画卯→Roll Call，×Mark Mao；平安→Peace，×Ping'an）；通名实体化幻觉（年年≠Niannian；岁月长安≠Chang'an；紫色团花=purple flower，×Epic Flower）〔LQE报告〕
-• 玩法规则文本逐条核：数值/上限/门槛（铜筹折算上限2000）、阶段流程序、机制词（多轮循环=Round-robin，×Rotating）、奖励归属与返还条件——客户一律 Critical〔LQE报告〕
-• 操作指引动作语义：技能效果的对象与方式（复原巨石使其停下≠restore…to a halt；招式=any attack，×a Move）〔LQE报告〕
-• 价格/概率语义词不可丢：折扣价、有机会获得（Cri 例：源「有机会获得[68金币]」译 contains）；回復≠receive〔LQE报告〕
-• 升 Cri 信号：误导玩家决策的规则文/题目-答案失配/占位符语义错位/经济敏感〔LQE报告〕</t>
+          <t>• 专有名词与普通词语的双向误判：拼音残留（“画卯”应译 Roll Call，误译 Mark Mao，第 105 段；“平安”应译 Peace，误译 Ping'an，第 54 段）；普通词语误作专名（“年年”误译为人名 Niannian，第 61 段；“岁月长安”误关联城市名 Chang'an，第 55 段；“紫色团花”应译 purple flower，误译 Epic Flower，第 293 段）〔LQE报告〕
+• 玩法规则文本逐条核对：数值与上限（“铜筹折算上限 2000”，第 258 段）、阶段流程、机制用语（“多轮循环”修订为 Round-robin，第 258 段）、奖励归属与返还条件；报告中规则说明类错译 7 条全部评为 Critical〔LQE报告〕
+• 操作指引的动作语义：技能效果的对象与方式（“复原巨石使其停止”，第 302 段；“招式”应译 any attack，误译 a Move，第 290 段）〔LQE报告〕
+• 价格类限定语不可缺失：“折扣价格 2 音玉”译文缺失“折扣”含义，评为 Major（第 14 段）；错误定义表 Critical 示例：源文“有机会获得[68金币]”译为 contains [68 Gold]〔LQE报告〕
+• 评为 Critical 的常见情形（依据报告判级归纳）：误导玩家决策的规则文本、题目与答案对应关系被破坏、占位符语义错位、涉及付费或收益的内容〔LQE报告归纳〕</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Min=误读但贴近源｜Maj=译错（关卡→Close Card）｜Cri=日期/规则/内容错致投诉法务</t>
+          <t>Minor＝误读但贴近源文｜Major＝译错（示例：关卡→Close Card）｜Critical＝日期、规则、内容错误以致引起投诉或法律风险</t>
         </is>
       </c>
     </row>
@@ -2116,13 +2130,13 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>• 限定词清点：任意/1次/仅/同时/最高/每（近失例：a Sword Trial 丢「任意」）〔LQE报告〕
-• 进度/资格条件（充值/达标/解锁）丢失即 Cri〔LQE报告〕</t>
+          <t>• 限定词逐一核对：任意、1 次、仅、同时、最高、每。相关案例：“任意试剑”译为 a Sword Trial，修订为 any Sword Trial（第 83 段，该条报告归入 Inconsistency Minor）〔LQE报告〕
+• 影响进度或资格的关键信息（如充值条件）缺失即 Critical〔LQE报告〕</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Min=丢衔接词｜Maj=丢改义成分（范围内的敌人→all enemies）｜Cri=丢进度资格关键信息</t>
+          <t>Minor＝缺失衔接词｜Major＝缺失改变语义的成分（“范围内的敌人”译为 all enemies）｜Critical＝缺失影响进度或资格的关键信息</t>
         </is>
       </c>
     </row>
@@ -2152,13 +2166,13 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>• 贴源过译与偏离区分〔LQE报告〕
-• 勿引入不存在的玩法元素（单体伤害→all enemies）〔LQE报告〕</t>
+          <t>• 区分贴近源文的过度翻译与偏离源文的添加〔LQE报告〕
+• 不得引入源文不存在的玩法元素（单体伤害译为 all enemies）〔LQE报告〕</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Min=过译仍贴源｜Maj=偏离源｜Cri=引入不存在玩法元素/招致投诉破坏沉浸</t>
+          <t>Minor＝过度翻译但仍贴近源文｜Major＝偏离源文｜Critical＝引入不存在的玩法元素或引起投诉、破坏沉浸</t>
         </is>
       </c>
     </row>
@@ -2178,22 +2192,22 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>始终Maj</t>
+          <t>强制 Major</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>0（pre-check 拦截）</t>
+          <t>0（确定性检查已可检出）</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>• 拼音输出≠已翻译——按 Mistranslation Cri 处理（N1）〔LQE报告〕</t>
+          <t>• 拼音转写不视为已翻译：报告将此类情形判入 Mistranslation Critical（见 N1）〔LQE报告〕</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>始终 Major</t>
+          <t>一律 Major</t>
         </is>
       </c>
     </row>
@@ -2213,28 +2227,28 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>始终Maj</t>
+          <t>强制 Major</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Maj12(+8rep)＝第二失分源</t>
+          <t>Major 12（另重复 8）；第二大罚分来源</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>• 活动/玩法/界面入口名逐字对官方库与已上线译名：皇宫寻宝=Imperial Palace Treasure Hunt（自创=Maj）；御前练兵=Imperial Drill〔LQE报告〕
-• 成对称号体系成对取：新锐|新兵=Recruit／老将|老兵=Veteran（×New Edge/Old General）〔LQE报告〕
-• 人名代号查角色档：青=Halcyon（×Qing 直拼）〔LQE报告〕
-• 同物跨段同名：手札统一 Journal（×Note）〔LQE报告〕
-• 过度术语化=错：通名勿造专名（异色灵蝶=strangely colored butterflies，×Spectral Butterfly）〔LQE报告〕
-• 系列名格式：赋神·乘桴归梦=Fu Shen - Rippling Dream（系列前缀保留；·→" - "）〔LQE报告＋Skill〕
-• 强制定译 19 条见 projects/wwm/adjudications.md《0512 裁决》〔LQE报告〕；泛词命中按语境甄别〔Skill 沿用〕</t>
+          <t>• 活动、玩法、界面入口名称逐字核对官方术语库及已上线译名：“皇宫寻宝”应译 Imperial Palace Treasure Hunt，自创译名评为 Major（第 2 段）；“御前练兵”应译 Imperial Drill（第 76 段）〔LQE报告〕
+• 成对称号按对应体系翻译：“新锐/新兵”＝Recruit，“老将/老兵”＝Veteran；误译 New Edge、Old General（第 366、367 段）〔LQE报告〕
+• 人物名称查角色档案：“青”＝Halcyon，不作拼音 Qing（第 194–201 段）〔LQE报告〕
+• 同一事物跨段落统一译名：“手札”统一为 Journal（第 198 段）〔LQE报告〕
+• 不得将通用名词自创为专有名词：“异色灵蝶”应译 strangely colored butterflies，误译 Spectral Butterfly（第 292 段）〔LQE报告〕
+• 系列名称格式：“赋神·乘桴归梦”＝Fu Shen - Rippling Dream，系列前缀保留（第 13 段）；间隔号“·”转写为“ - ”〔LQE报告＋Skill〕
+• 本报告确认的强制译名清单见 projects/wwm/adjudications.md《0512 裁决》〔LQE报告〕；通用词汇命中术语表时结合语境判断〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>始终 Major</t>
+          <t>一律 Major</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2260,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Inconsistency 一致性</t>
+          <t>Inconsistency 不一致</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -2259,19 +2273,19 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Min5(+2rep)</t>
+          <t>Minor 5（另重复 2）</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>• 平行句族统一句型：任务/成就列表同模板（Complete any X once with a Veteran/Recruit 族）〔LQE报告〕
-• 任务名引用格式统一（Lost Chapter quest: X）〔LQE报告〕
-• 涉术语表词条的冲突归 Terminology，其余归此〔Skill 沿用〕</t>
+          <t>• 平行句式统一句型：任务、成就列表采用同一模板（Complete any X once with a Veteran/Recruit，第 82–94 段；原译文 Team up with… and complete… 与之混用被判错）〔LQE报告〕
+• 任务名称引用格式统一（Lost Chapter quest: X，第 89 段）〔LQE报告〕
+• 涉及术语表词条的不一致归 Terminology，其余归本类〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Min=拼写大小写语气不一（approx./approximately 混用）｜Maj=术语混用致误解（hero/protagonist/main character）</t>
+          <t>Minor＝拼写、大小写、语气不统一（approx. 与 approximately 混用）｜Major＝术语混用以致误解（hero、protagonist、main character 混用）</t>
         </is>
       </c>
     </row>
@@ -2301,13 +2315,13 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>• 主谓一致/时态/冠词〔LQE报告〕
-• 占位符邻接可数名词用「{} day(s)」型复数〔LQE报告〕</t>
+          <t>• 主谓一致、时态、冠词（错误定义表示例）〔LQE报告〕
+• 占位符后接可数名词使用复数兼容写法（修订稿示例：{} in {} day(s)，第 107 段）〔LQE报告〕</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Min=显粗心（Me and my friends are…）｜Maj=损公信（The lego set are nice）｜Cri=灾难性后果</t>
+          <t>Minor＝显见疏忽（Me and my friends are…）｜Major＝损害可信度（The lego set are nice）｜Critical＝造成严重后果</t>
         </is>
       </c>
     </row>
@@ -2332,18 +2346,18 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>0（pre-check 盖大半）</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>• 半角标点、对齐源标点（pre-check 已盖大半）〔Skill 沿用〕
-• 长句逗号缺失影响可读性〔LQA模板〕</t>
+          <t>• 半角标点、与源文标点对齐（确定性检查已覆盖大部分）〔Skill 沿用〕
+• 长句缺少逗号影响可读性〔LQA模板〕</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Min=错但可懂｜Maj=改句意（Let's eat, Timmy→Let's eat Timmy）｜Cri=金额标点致事实错误</t>
+          <t>Minor＝错误但可理解｜Major＝改变句意（Let's eat, Timmy → Let's eat Timmy）｜Critical＝金额标点错误导致事实性错误</t>
         </is>
       </c>
     </row>
@@ -2373,13 +2387,13 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>• Equipments/Acheive/Entrence 型错拼〔LQE报告〕
-• 易混词 accept/except、then/than、your/you're=Maj〔LQE报告〕</t>
+          <t>• 拼写错误（错误定义表示例：Equipments、Acheive、Entrence）〔LQE报告〕
+• 易混词（accept/except、then/than、your/you're）＝Major〔LQE报告〕</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Min=粗心错拼｜Maj=损公信易混词｜Cri=灾难性（pubic library）</t>
+          <t>Minor＝一般拼写错误｜Major＝损害可信度的易混词｜Critical＝造成严重后果（示例：pubic library）</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2405,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Company style 公司风格</t>
+          <t>Company style 项目风格</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -2404,21 +2418,21 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Min12·Maj1</t>
+          <t>Minor 12、Major 1</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>• 句中通名小写：accept a quest / the treasure（×句中 Accept a Quest）〔LQE报告；Title/Sentence Mode 本体=Skill 沿用〕
-• 序号/卷号 Unicode 罗马数字（N3）〔LQE报告〕
-• 括号体系：设施/可放置物名 [Stove]（×「」原样、×#Y"X"#E 引号式）〔LQE报告〕
-• 诗句/banner 有押韵节奏重写权（九天阊阖联→bold/gold 韵对）；过度直译判此类〔LQE报告〕
-• 禁古英语/网络俚语/UI 语气进剧情；SG 明文违反才归此，无明文归 Unidiomatic〔Skill 沿用〕</t>
+          <t>• 句中普通名词小写：Accept a Quest 在句中修订为 accept a quest（第 155 段）；标题式大写仅用于标题位置〔LQE报告；大小写双模式规则为 Skill 沿用〕
+• 序号、卷号使用 Unicode 罗马数字（见 N3）〔LQE报告〕
+• 设施与可放置物名称使用方括号：修订稿统一为 [Stove]、[Dining Table] 等格式（第 260 段修订稿）〔LQE报告〕
+• 诗句、宣传语允许为押韵与节奏改写：第 249 段对仗句修订为 bold/gold 押韵句式；过度直译归入本类〔LQE报告〕
+• 语域错置（错误定义表 Major 示例：古代背景项目使用现代口语 Sup, Harry?）〔LQE报告〕；风格指南有明文规定的违例归本类，无明文的归 Unidiomatic〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Min=Oxford comma/大小写规则未循｜Maj=语域错置（古风项目用 Sup, Harry?）</t>
+          <t>Minor＝未遵循既定标点或大小写规范｜Major＝语域错置（古代背景使用现代口语）</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2444,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Unidiomatic 不合语言习惯</t>
+          <t>Unidiomatic 表达不自然</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -2443,19 +2457,19 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Min6(+11rep)</t>
+          <t>Minor 6（另重复 11）</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>• UI 短句自然化模板：Continue Completing &lt;X&gt;→Continue completing the X quest（去尖括号＋补通名 quest＋句子化大小写）——同一模式重复 12 次〔LQE报告〕
-• 直译腔标志：Warm Tips / Successfully Claimed 型〔LQE报告〕
-• 三档标尺：母语者难懂／直译但可懂／好文笔——仅前两档计错〔LQA模板，新增〕</t>
+          <t>• 界面短句的自然化处理：Continue Completing &lt;X&gt; 统一修订为 Continue completing the X quest（去除尖括号、补充通名 quest、改句式大小写；第 17–28 段，同一问题出现 12 次）〔LQE报告〕
+• 直译腔的典型形式（错误定义表示例：Warm Tips、Successfully Claimed）〔LQE报告〕
+• 自然度三级标尺：母语者难以理解／直译但可理解／自然流畅，仅前两级计错〔LQA模板，新增〕</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Min=不地道但可懂（Successfully Claimed）｜Maj=不地道且致困惑（Warm Tips）｜Cri=冒犯或彻底破坏沉浸（You no go. I go for you!）</t>
+          <t>Minor＝不地道但可理解（Successfully Claimed）｜Major＝不地道且引起困惑（Warm Tips）｜Critical＝冒犯或完全破坏沉浸（You no go. I go for you!）</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2481,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Locale convention 语言环境约定</t>
+          <t>Locale convention 区域格式</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -2485,25 +2499,25 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>• 日期防歧义拼写月份（6/5/2023→May 6, 2023）〔LQE报告〕
+          <t>• 日期写法避免歧义（错误定义表示例：6/5/2023 应拼写月份）〔LQE报告〕
 • 货币符号与币种一致〔LQE报告〕</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Min=格式少见仍可懂｜Maj=影响理解｜Cri=币种错（¥299→$299）致法务/财务风险</t>
+          <t>Minor＝格式少见但可理解｜Major＝影响理解｜Critical＝币种错误（人民币 299 元误写为 $299）导致法律或财务风险</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Audience Appropriateness（客户父类=Verity）</t>
+          <t>Audience Appropriateness（客户定义表上级类别名为 Verity）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Culture specific reference 文化特定所指</t>
+          <t>Culture specific reference 文化特定指涉</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2521,13 +2535,13 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>• 源文化梗错置目标受众（520、圣诞吃苹果）〔LQE报告〕
-• 冒犯/涉政/禁忌=Cri〔LQE报告〕</t>
+          <t>• 源语文化元素错置于目标受众（错误定义表示例：520、圣诞节吃苹果）〔LQE报告〕
+• 冒犯性或涉敏内容＝Critical〔LQE报告〕</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Min=文化梗略怪｜Maj=过于小众致困惑｜Cri=冒犯/政治敏感</t>
+          <t>Minor＝文化指涉略显突兀｜Major＝过于小众以致困惑｜Critical＝冒犯或涉及敏感议题</t>
         </is>
       </c>
     </row>
@@ -2552,17 +2566,17 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0（本 skill 独有子类）</t>
+          <t>0（现行体系独有子类）</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>• 语域/世界观口吻（仙侠敬语→现代俚语）；准确但不合受众期待〔Skill 沿用〕</t>
+          <t>• 语域与世界观语气（如武侠语境使用现代俚语）；翻译准确但不符合目标受众预期〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>参照 Company style/Unidiomatic 梯度按影响定级</t>
+          <t>参照 Company style 与 Unidiomatic 的分级按影响程度判定</t>
         </is>
       </c>
     </row>
@@ -2582,22 +2596,22 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>始终Maj</t>
+          <t>强制 Major</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0（pre-check 盖）</t>
+          <t>0（确定性检查已覆盖）</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>• 色标相对位置、{} 数量与顺序、\n 保留〔Skill 沿用〕</t>
+          <t>• 颜色标签相对位置、占位符数量与顺序、换行符保留〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>始终 Major</t>
+          <t>一律 Major</t>
         </is>
       </c>
     </row>
@@ -2617,22 +2631,22 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>始终Maj</t>
+          <t>强制 Major</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>0（pre-check 盖）</t>
+          <t>0（确定性检查已覆盖）</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>• max-length 列优先；超长截断风险〔Skill 沿用〕</t>
+          <t>• 优先使用 max-length 列；超长存在截断风险〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>始终 Major</t>
+          <t>一律 Major</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2676,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>• 兜底；先过单一归属表再落此〔Skill 沿用〕</t>
+          <t>• 未尽事项；先经单一归属规则核对后方可归入本类〔Skill 沿用〕</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">

--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -813,422 +813,597 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>通用评估原则（评估每条错误前先行核对）</t>
+          <t>应用状态与主要差异（摘要）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>原则</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>来源</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>应用状态：本清单尚未接入评估流程，当前为参考文档。已生效的仅有 projects/wwm/adjudications.md 中归档的 0512 裁决（评估前必读文件，下次评估自动注入）；其余新增内容均待批准实施，见“后续实施事项”</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>三点法则</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>译文同时满足准确（核心含义保留）、合规（符合风格指南、项目指令与术语表）、合乎语法三项，即视为正确；偏好性改写不计为错误，至多记 Neutral 建议</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>LQA模板原文（新增）</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>方面</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>现行体系</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>本清单方案</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>依据</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>单一归属与从重判定</t>
+          <t>重复错误计分</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>每条错误只归入一个类别，取最具体的一类；严重度在 Minor 与 Major 之间无法确定时，判 Major</t>
+          <t>每次出现均全额计分；报告输出虽含 repeated 列但数值恒为 0，无识别逻辑</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Skill 沿用</t>
+          <t>仅首次计分，重复予以记录不计罚分</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>LQE 报告评分卡复核（34 条重复错误未计入罚分）。现行算法在重复较多的文件上得分将低于客户口径</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Word Choice 判定边界</t>
+          <t>成组文本</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>用词导致含义错误的，归 Mistranslation；含义正确但存在更优用词的，归 Unidiomatic（Minor）或记 Neutral。前半句为 LQA 模板原文；归入 Unidiomatic/Neutral 系本清单适配（现行体系无 Word Choice 类别）</t>
+          <t>逐段独立评估</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>LQA模板＋本清单适配</t>
+          <t>对联、题目类文本按组评估</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>本次 41 条 Critical 中 26 条源于成对短句被逐句独立直译</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>严重度三级判定基准</t>
+          <t>AI 评估视角</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Minor＝可察觉但不致误导；Major＝很可能误导玩家或损害可信度；Critical＝可能引起投诉、法律风险、功能破坏或出现在高可见位置。系对三处定义的综合转述，非逐字引用</t>
+          <t>仅依据错误分类定义</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Skill＋LQE报告定义表＋LQA模板综合</t>
+          <t>注入人工评审实判模式（拼音残留、规则文本从严、平行句式统一、不得自创术语等）</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>“AI评估项17子类”工作表各子类评估关注点</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>误报防控</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>无明文规则</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>三点法则与 Word Choice 判定边界</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>LQA 模板原文</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>计分与流程规则</t>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>确定性检查</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>13 项</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>新增拼音残留、同源异译、罗马数字 3 项检查及重复计分规则</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>“确定性检查项”工作表 N1–N4</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>通过阈值</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>单一阈值 98</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>按交付阶段分级：TEP/MTPE 98，润色/二审 99</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>LQE 报告错误定义表</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>总体评价：现行体系在格式类确定性检查上覆盖充分（本次报告该类错误为零）；客户罚分的 85.6% 集中于语义与成组结构层面，本清单的调整方向即为将评估重心移向该层面</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>通用评估原则（评估每条错误前先行核对）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>原则</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>核验依据</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>重复错误</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>重复错误予以记录（Repeated=YES）但不计罚分，仅首次计分</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>LQE报告（新增）</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>评分卡复核：罚分 610 恰等于非重复错误之和（25×1＋35×5＋41×10），34 条重复错误未计入</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>阈值分级</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>TEP、MTPE 阈值 98；润色、二审阈值 99</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>LQE报告（新增）</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>错误定义表原文（0.98／0.99）；现行 profile.threshold 参数已支持配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>严重度分值</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Neutral 0／Minor 1／Major 5／Critical 10</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Skill 沿用</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>与 LQE 报告 Error Severity 工作表一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>评分公式</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>得分＝1－加权罚分合计÷词数</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Skill 沿用</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>错误定义表原文 Score = 1 - Penalty total/Wordcount；按报告数据复核（1－915÷5314＝82.78）一致</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>成组文本评估</t>
+          <t>三点法则</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>对联、题目、谜题类文本按组评估：上下联对仗与押韵、题目与答案的对应关系须保持；逐句独立直译将破坏成组结构</t>
+          <t>译文同时满足准确（核心含义保留）、合规（符合风格指南、项目指令与术语表）、合乎语法三项，即视为正确；偏好性改写不计为错误，至多记 Neutral 建议</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>本清单依据 LQE 报告归纳（新增）</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>26 条成对短句 Critical 的修订稿呈两两押韵模式；报告未附判定理由，成因系归纳推断</t>
+          <t>LQA模板原文（新增）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>文本类型与判级倾向</t>
+          <t>单一归属与从重判定</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>规则说明类错译普遍判 Critical；界面短句问题多归 Unidiomatic 或 Company style；诗句宣传语按风格改写要求评估</t>
+          <t>每条错误只归入一个类别，取最具体的一类；严重度在 Minor 与 Major 之间无法确定时，判 Major</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>本清单依据 LQE 报告判级分布归纳（新增）</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>规则说明类错译 7 条均为 Critical；界面短句 12 条均为 Unidiomatic Minor</t>
+          <t>Skill 沿用</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>Word Choice 判定边界</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>用词导致含义错误的，归 Mistranslation；含义正确但存在更优用词的，归 Unidiomatic（Minor）或记 Neutral。前半句为 LQA 模板原文；归入 Unidiomatic/Neutral 系本清单适配（现行体系无 Word Choice 类别）</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>LQA模板＋本清单适配</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>严重度三级判定基准</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Minor＝可察觉但不致误导；Major＝很可能误导玩家或损害可信度；Critical＝可能引起投诉、法律风险、功能破坏或出现在高可见位置。系对三处定义的综合转述，非逐字引用</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Skill＋LQE报告定义表＋LQA模板综合</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>计分与流程规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>核验依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>重复错误</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>重复错误予以记录（Repeated=YES）但不计罚分，仅首次计分</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>LQE报告（新增）</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>评分卡复核：罚分 610 恰等于非重复错误之和（25×1＋35×5＋41×10），34 条重复错误未计入</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>阈值分级</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>TEP、MTPE 阈值 98；润色、二审阈值 99</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>LQE报告（新增）</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>错误定义表原文（0.98／0.99）；现行 profile.threshold 参数已支持配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>严重度分值</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Neutral 0／Minor 1／Major 5／Critical 10</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Skill 沿用</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>与 LQE 报告 Error Severity 工作表一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>评分公式</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>得分＝1－加权罚分合计÷词数</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Skill 沿用</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>错误定义表原文 Score = 1 - Penalty total/Wordcount；按报告数据复核（1－915÷5314＝82.78）一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>成组文本评估</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>对联、题目、谜题类文本按组评估：上下联对仗与押韵、题目与答案的对应关系须保持；逐句独立直译将破坏成组结构</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>本清单依据 LQE 报告归纳（新增）</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>26 条成对短句 Critical 的修订稿呈两两押韵模式；报告未附判定理由，成因系归纳推断</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>文本类型与判级倾向</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>规则说明类错译普遍判 Critical；界面短句问题多归 Unidiomatic 或 Company style；诗句宣传语按风格改写要求评估</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>本清单依据 LQE 报告判级分布归纳（新增）</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>规则说明类错译 7 条均为 Critical；界面短句 12 条均为 Unidiomatic Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
           <t>报告格式解析</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>修订列可为 #N/A（审校未提供修订稿）；重复列取值 YES/NO</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>LQE报告（新增）</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>第 259 段修订列为 #N/A</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>后续实施事项</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>事项</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>涉及文件</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
+    <row r="56">
+      <c r="A56" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>重复错误计分规则（N4）</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_calc.py</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>待批准</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
+    <row r="57">
+      <c r="A57" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>拼音残留检查（N1）、同源异译检查（N2）</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_io.py</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>待批准</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
+    <row r="58">
+      <c r="A58" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>罗马数字检查（N3）</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>projects/wwm/checks.json</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>待批准</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="n">
+    <row r="59">
+      <c r="A59" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>0512 报告术语与风格裁决归档</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>projects/wwm/adjudications.md</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>已完成（2026-06-11）</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="n">
+    <row r="60">
+      <c r="A60" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>评估流程引用本清单</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>SKILL.md</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>待批准</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="n">
+    <row r="61">
+      <c r="A61" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>题目类文本按组送评（同组段落合并提供评估上下文）</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_io.py 及评估流程</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>待批准；建议在下一批题目表评估前完成</t>
         </is>

--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>应用状态：本清单尚未接入评估流程，当前为参考文档。已生效的仅有 projects/wwm/en/adjudications.md 中归档的 0512 裁决（评估前必读文件，下次评估自动注入）；其余新增内容均待批准实施，见“后续实施事项”</t>
+          <t>应用状态：N5–N9 及 PM 反馈 #3/#7/#10 已实施（2026-06-12）；projects/wwm/en/adjudications.md 的 0512 裁决已归档生效；N1–N4 仍待批准。原说明：已生效的 0512 裁决（评估前必读文件，下次评估自动注入）；其余新增内容均待批准实施，见“后续实施事项”</t>
         </is>
       </c>
     </row>
@@ -1406,6 +1406,46 @@
       <c r="D61" s="5" t="inlineStr">
         <is>
           <t>待批准；建议在下一批题目表评估前完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>PM 反馈新增检查 N5–N9 及 #3/#7/#10（详见《PM反馈检查项修改报告》）</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py、SKILL.md、languages/</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>已完成（2026-06-12，PM 批准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>异源同译长度分档（≥20 字才报，PM 已拍板）</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>随事项 2 的 N2 实施</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>待实施（参数已定）</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2134,40 +2174,376 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>terminal_punct</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>句尾终止标点不对齐</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Punctuation</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>PM反馈#1</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>源以终止标点结尾而译文句尾无（.!?…），或源无句尾标点而译文添加句号；句中标点数量交 AI 评估；无句号体系语言（th）由语言属性自动关闭</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>cn_numbers</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>中文数字+量词漏译</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Mistranslation</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>PM反馈#2</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>仅「中文数字+量词」强模式触发（含「一」）；译侧接受阿拉伯数字、英文数词、泰文数字与泰语数词</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>word_repeat</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>单词连续重复</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>PM反馈#6</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>the the 类；白名单豁免合法重复；非空格分词语言由语言属性自动关闭</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>intra_word_case</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>词内大小写混乱</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Spelling</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PM反馈#8</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>AppLe 类词内转折；豁免术语表词形/Mc/iPhone 型/PvP 型/标签变量；非拉丁语言自动关闭</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>paired_punct</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>半角成对标点不完整</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Punctuation</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>PM反馈#9</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>()、[]、直双引号奇偶；源侧平衡而译侧不平衡才报；撇号豁免；全角/弯引号由现行全角标点检查拦截</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>tag_count</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>通用标签数量对账</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Markup</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PM反馈#3</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>&lt;…&gt;、[…] 模式源译数量比对兜底；项目专属格式用 checks.json custom type=count_match 精配</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>term_case</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>术语全大写缩写大小写</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Company style</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>PM反馈#7</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>术语表词条含 HP/ATK 类全大写缩写而译文大小写不符；PM 裁决仅查缩写、判严重；非拉丁语言自动关闭</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>ellipsis_mix</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>省略号样式混用</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Inconsistency</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PM反馈#10</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>PM 裁决一个项目只用一种省略号；文件内 … 与 ... 并存时少数派段报</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py（已实施 2026-06-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>repeat_dedup</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>重复错误计分规则</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>（计分规则）</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>新增·LQE报告</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>重复出现的同一错误仅首次计罚分，其余标记 Repeated 不计分。依据：报告 34 条重复标记错误经评分卡复核均未计入罚分。重复判定条件（相同源文、相同译文、相同错误）系依据报告数据归纳，报告未明文定义</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_calc.py（待批准）</t>
         </is>

--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -820,7 +820,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>应用状态：N5–N9 及 PM 反馈 #3/#7/#10 已实施（2026-06-12）；projects/wwm/en/adjudications.md 的 0512 裁决已归档生效；N1–N4 仍待批准。原说明：已生效的 0512 裁决（评估前必读文件，下次评估自动注入）；其余新增内容均待批准实施，见“后续实施事项”</t>
+          <t>应用状态：全部确定性检查 N1–N9 及 PM 反馈 #3/#7/#10 已实施（2026-06-12）；N4 重复计分已入 lqe_calc；成组送评与清单引用已接入 SKILL.md。0512 裁决（评估前必读文件）持续生效</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>待批准</t>
+          <t>已完成（2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -1315,17 +1315,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>拼音残留检查（N1）、同源异译检查（N2）</t>
+          <t>拼音残留检查（N1）、同源异译检查（N2，含 ≥20 字分档）</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py</t>
+          <t>scripts/lqe_checks.py</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>待批准</t>
+          <t>已完成（2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>待批准</t>
+          <t>已完成（2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>待批准</t>
+          <t>已完成（2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>题目类文本按组送评（同组段落合并提供评估上下文）</t>
+          <t>题目类文本按组送评（read --group-col + SKILL.md 合并评估指引）</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py 及评估流程</t>
+          <t>scripts/lqe_io.py、SKILL.md</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>待批准；建议在下一批题目表评估前完成</t>
+          <t>已完成（2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>待实施（参数已定）</t>
+          <t>已完成（2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>译文中出现两个以上连续拼音音节构成的词，且不在官方保留拼音名单内（报告修订稿保留 Kaifeng、Qinghe、Jianghu、Fu Shen 等）。报告实例：“画卯”译为 Mark Mao（第 105 段）、“平安”译为 Ping'an（第 54 段），均评为 Critical。属半确定性检查：正则初筛后须人工或 AI 复核</t>
+          <t>已实施（2026-06-12，确定性层抓强特征：大写头+≥2音节+zh/x/q 或撇号分隔；TB 词形豁免；弱信号由 AI 评估关注点覆盖）。报告实例：“画卯”译为 Mark Mao（第 105 段）、“平安”译为 Ping'an（第 54 段），均评为 Critical。属半确定性检查：正则初筛后须人工或 AI 复核</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py（待批准）</t>
+          <t>scripts/lqe_checks.py（已实施 2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>同一文件内相同源文对应不同译文；以及相同译文对应不同源文。系报告 Inconsistency 类错误（第 82–94 段）中可程序化检出的子集</t>
+          <t>同一文件内相同源文对应不同译文；以及相同译文对应不同源文。系报告 Inconsistency 类错误（第 82–94 段）中可程序化检出的子集。已实施（2026-06-12）：双向检出，异源同译仅当涉及源文全部 ≥20 字（PM 拍板）；组内首段为基准不报</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py（待批准）</t>
+          <t>scripts/lqe_checks.py（已实施 2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>projects/wwm/en/checks.json（待批准）</t>
+          <t>projects/wwm/en/checks.json（已实施 2026-06-12）</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_calc.py（待批准）</t>
+          <t>scripts/lqe_calc.py（已实施 2026-06-12，--no-repeat-dedup 可关）</t>
         </is>
       </c>
     </row>

--- a/docs/质量检查项清单.xlsx
+++ b/docs/质量检查项清单.xlsx
@@ -510,7 +510,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>〔Skill〕现行评估体系 SKILL.md：确定性检查 13 项、错误子类 17 项、权重与强制严重度、评分公式、归类规则</t>
+          <t>〔Skill〕评估体系 SKILL.md：本清单撰写时确定性检查 13 项（2026-06-12 已扩至 23 项）、错误子类 17 项、权重与强制严重度、评分公式、归类规则</t>
         </is>
       </c>
     </row>
@@ -942,17 +942,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>13 项</t>
+          <t>撰写时 13 项，现 23 项</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>新增拼音残留、同源异译、罗马数字 3 项检查及重复计分规则</t>
+          <t>N1–N4 及 PM 反馈新增项均已实施（2026-06-12）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>“确定性检查项”工作表 N1–N4</t>
+          <t>“确定性检查项”工作表</t>
         </is>
       </c>
     </row>
